--- a/Indicator_4/Real_data/White_Marlin_Atl.xlsx
+++ b/Indicator_4/Real_data/White_Marlin_Atl.xlsx
@@ -1,22 +1,294 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4EA0BC-9BE4-4CD0-821B-D081DCF340F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>White_Marlin_Atl</t>
+  </si>
+  <si>
+    <t>E.g. 'Swordfish_Natl'</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>max_age</t>
+  </si>
+  <si>
+    <t>14.979</t>
+  </si>
+  <si>
+    <t>Age to 5% natural survival</t>
+  </si>
+  <si>
+    <t>Life history</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>von Bertalannfy K</t>
+  </si>
+  <si>
+    <t>Linf</t>
+  </si>
+  <si>
+    <t>0.932</t>
+  </si>
+  <si>
+    <t>von Bertalannfy L-infinity (asymptotic length)</t>
+  </si>
+  <si>
+    <t>L50_Linf</t>
+  </si>
+  <si>
+    <t>172.1</t>
+  </si>
+  <si>
+    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+  </si>
+  <si>
+    <t>Total_L5_L50</t>
+  </si>
+  <si>
+    <t>0.673</t>
+  </si>
+  <si>
+    <t>Length at 5% selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Fleet selectivity</t>
+  </si>
+  <si>
+    <t>All fleets combined</t>
+  </si>
+  <si>
+    <t>Total_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.989</t>
+  </si>
+  <si>
+    <t>Length at full selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Total_VML</t>
+  </si>
+  <si>
+    <t>0.962</t>
+  </si>
+  <si>
+    <t>Selectivity of maximum length class</t>
+  </si>
+  <si>
+    <t>Fleet_1_L5_L50</t>
+  </si>
+  <si>
+    <t>0.671</t>
+  </si>
+  <si>
+    <t>Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet_1_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.984</t>
+  </si>
+  <si>
+    <t>Fleet_1_VML</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Fleet_2_L5_L50</t>
+  </si>
+  <si>
+    <t>0.892</t>
+  </si>
+  <si>
+    <t>Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_2_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>Fleet_2_VML</t>
+  </si>
+  <si>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>Fleet_3_L5_L50</t>
+  </si>
+  <si>
+    <t>0.699</t>
+  </si>
+  <si>
+    <t>Fleet 3</t>
+  </si>
+  <si>
+    <t>Fleet_3_LFS_L50</t>
+  </si>
+  <si>
+    <t>Fleet_3_VML</t>
+  </si>
+  <si>
+    <t>Fleet_1_CF</t>
+  </si>
+  <si>
+    <t>0.939</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet catch scale</t>
+  </si>
+  <si>
+    <t>Fleet_2_CF</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_3_CF</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 3</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Total_catch</t>
+  </si>
+  <si>
+    <t>Total_mean_len</t>
+  </si>
+  <si>
+    <t>Total_mean_age</t>
+  </si>
+  <si>
+    <t>Total_CV_len</t>
+  </si>
+  <si>
+    <t>Total_frac_mat</t>
+  </si>
+  <si>
+    <t>Total_Index</t>
+  </si>
+  <si>
+    <t>Fleet_1_catch</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_1_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_1_Index</t>
+  </si>
+  <si>
+    <t>Fleet_2_catch</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_2_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_2_Index</t>
+  </si>
+  <si>
+    <t>Fleet_3_catch</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_3_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_3_Index</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +336,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +388,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +422,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +457,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,656 +633,365 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>White_Marlin_Atl</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Genus specius</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Billfish</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>North Atlantic</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>max_age</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>14.979</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Age to 5% natural survival</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>von Bertalannfy K</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>L50_Linf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.932</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>All_L5_L50</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.673</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>All_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.989</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>All_VML</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.962</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fleet_1_L5_L50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.671</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fleet_1_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.984</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fleet_1_VML</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fleet_2_L5_L50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.892</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fleet_2_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fleet_2_VML</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0.085</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fleet_3_L5_L50</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.699</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fleet_3_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0.984</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fleet_3_VML</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>All_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.967</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fleet_1_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.895</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fleet_2_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.003</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fleet_3_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.004</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fleet_1_CF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.939</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fleet_2_CF</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0.022</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Fleet_3_CF</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0.039</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1009,138 +1000,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_catch</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_len</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_age</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total_CV_len</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total_frac_mat</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Index</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_catch</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_len</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_age</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_CV_len</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_frac_mat</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_Index</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_catch</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_len</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_age</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_CV_len</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_frac_mat</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_Index</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_catch</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_len</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_age</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_CV_len</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_frac_mat</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1956</v>
       </c>
@@ -1148,7 +1089,7 @@
         <v>19</v>
       </c>
       <c r="G2">
-        <v>3.013</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="H2">
         <v>19</v>
@@ -1160,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1957</v>
       </c>
@@ -1168,7 +1109,7 @@
         <v>160</v>
       </c>
       <c r="G3">
-        <v>3.013</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="H3">
         <v>160</v>
@@ -1180,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1958</v>
       </c>
@@ -1188,7 +1129,7 @@
         <v>161</v>
       </c>
       <c r="G4">
-        <v>3.013</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="H4">
         <v>161</v>
@@ -1200,7 +1141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1959</v>
       </c>
@@ -1208,7 +1149,7 @@
         <v>112</v>
       </c>
       <c r="G5">
-        <v>3.011</v>
+        <v>3.0110000000000001</v>
       </c>
       <c r="H5">
         <v>112</v>
@@ -1220,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0.242</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>0.24199999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1960</v>
       </c>
@@ -1231,7 +1172,7 @@
         <v>313</v>
       </c>
       <c r="G6">
-        <v>2.991</v>
+        <v>2.9910000000000001</v>
       </c>
       <c r="H6">
         <v>253</v>
@@ -1243,10 +1184,10 @@
         <v>60</v>
       </c>
       <c r="Y6">
-        <v>0.408</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>0.40799999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1961</v>
       </c>
@@ -1269,7 +1210,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1962</v>
       </c>
@@ -1277,7 +1218,7 @@
         <v>2064</v>
       </c>
       <c r="G8">
-        <v>2.962</v>
+        <v>2.9620000000000002</v>
       </c>
       <c r="H8">
         <v>1985</v>
@@ -1289,10 +1230,10 @@
         <v>79</v>
       </c>
       <c r="Y8">
-        <v>2.018</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>2.0179999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1963</v>
       </c>
@@ -1300,7 +1241,7 @@
         <v>2614</v>
       </c>
       <c r="G9">
-        <v>2.928</v>
+        <v>2.9279999999999999</v>
       </c>
       <c r="H9">
         <v>2548</v>
@@ -1315,7 +1256,7 @@
         <v>1.921</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1964</v>
       </c>
@@ -1323,7 +1264,7 @@
         <v>3735</v>
       </c>
       <c r="G10">
-        <v>2.832</v>
+        <v>2.8319999999999999</v>
       </c>
       <c r="H10">
         <v>3661</v>
@@ -1335,10 +1276,10 @@
         <v>74</v>
       </c>
       <c r="Y10">
-        <v>1.515</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1.5149999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1965</v>
       </c>
@@ -1346,7 +1287,7 @@
         <v>4906</v>
       </c>
       <c r="G11">
-        <v>2.592</v>
+        <v>2.5920000000000001</v>
       </c>
       <c r="H11">
         <v>4827</v>
@@ -1358,10 +1299,10 @@
         <v>79</v>
       </c>
       <c r="Y11">
-        <v>1.362</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>1.3620000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1966</v>
       </c>
@@ -1369,7 +1310,7 @@
         <v>3513</v>
       </c>
       <c r="G12">
-        <v>2.308</v>
+        <v>2.3079999999999998</v>
       </c>
       <c r="H12">
         <v>3425</v>
@@ -1381,10 +1322,10 @@
         <v>88</v>
       </c>
       <c r="Y12">
-        <v>1.616</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>1.6160000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1967</v>
       </c>
@@ -1407,7 +1348,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1968</v>
       </c>
@@ -1415,7 +1356,7 @@
         <v>2049</v>
       </c>
       <c r="G14">
-        <v>1.441</v>
+        <v>1.4410000000000001</v>
       </c>
       <c r="H14">
         <v>1949</v>
@@ -1427,10 +1368,10 @@
         <v>100</v>
       </c>
       <c r="Y14">
-        <v>1.582</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>1.5820000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1969</v>
       </c>
@@ -1438,7 +1379,7 @@
         <v>2272</v>
       </c>
       <c r="G15">
-        <v>1.174</v>
+        <v>1.1739999999999999</v>
       </c>
       <c r="H15">
         <v>2171</v>
@@ -1450,10 +1391,10 @@
         <v>101</v>
       </c>
       <c r="Y15">
-        <v>1.432</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>1.4319999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1970</v>
       </c>
@@ -1461,13 +1402,13 @@
         <v>2147</v>
       </c>
       <c r="C16">
-        <v>167.433</v>
+        <v>167.43299999999999</v>
       </c>
       <c r="E16">
-        <v>0.168</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="F16">
-        <v>0.473</v>
+        <v>0.47299999999999998</v>
       </c>
       <c r="G16">
         <v>1.161</v>
@@ -1476,13 +1417,13 @@
         <v>2027</v>
       </c>
       <c r="I16">
-        <v>167.433</v>
+        <v>167.43299999999999</v>
       </c>
       <c r="K16">
-        <v>0.168</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="L16">
-        <v>0.473</v>
+        <v>0.47299999999999998</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1491,10 +1432,10 @@
         <v>120</v>
       </c>
       <c r="Y16">
-        <v>1.027</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>1.0269999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1971</v>
       </c>
@@ -1502,7 +1443,7 @@
         <v>2266</v>
       </c>
       <c r="C17">
-        <v>162.442</v>
+        <v>162.44200000000001</v>
       </c>
       <c r="E17">
         <v>0.105</v>
@@ -1511,19 +1452,19 @@
         <v>0.435</v>
       </c>
       <c r="G17">
-        <v>1.086</v>
+        <v>1.0860000000000001</v>
       </c>
       <c r="H17">
         <v>2153</v>
       </c>
       <c r="I17">
-        <v>161.158</v>
+        <v>161.15799999999999</v>
       </c>
       <c r="K17">
-        <v>0.149</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="L17">
-        <v>0.366</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1535,16 +1476,16 @@
         <v>163.726</v>
       </c>
       <c r="W17">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="X17">
         <v>0.503</v>
       </c>
       <c r="Y17">
-        <v>1.029</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>1.0289999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1972</v>
       </c>
@@ -1552,28 +1493,28 @@
         <v>2289</v>
       </c>
       <c r="C18">
-        <v>161.461</v>
+        <v>161.46100000000001</v>
       </c>
       <c r="E18">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="F18">
-        <v>0.404</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="G18">
-        <v>0.991</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="H18">
         <v>2171</v>
       </c>
       <c r="I18">
-        <v>158.538</v>
+        <v>158.53800000000001</v>
       </c>
       <c r="K18">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="L18">
-        <v>0.234</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -1582,19 +1523,19 @@
         <v>118</v>
       </c>
       <c r="U18">
-        <v>164.384</v>
+        <v>164.38399999999999</v>
       </c>
       <c r="W18">
-        <v>0.067</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="X18">
-        <v>0.574</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="Y18">
-        <v>0.841</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>0.84099999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1973</v>
       </c>
@@ -1602,16 +1543,16 @@
         <v>1868</v>
       </c>
       <c r="C19">
-        <v>158.278</v>
+        <v>158.27799999999999</v>
       </c>
       <c r="E19">
-        <v>0.082</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="F19">
-        <v>0.369</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="G19">
-        <v>0.912</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="H19">
         <v>1750</v>
@@ -1620,10 +1561,10 @@
         <v>152.297</v>
       </c>
       <c r="K19">
-        <v>0.096</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="L19">
-        <v>0.211</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -1632,19 +1573,19 @@
         <v>118</v>
       </c>
       <c r="U19">
-        <v>164.259</v>
+        <v>164.25899999999999</v>
       </c>
       <c r="W19">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="X19">
-        <v>0.527</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="Y19">
         <v>0.998</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1974</v>
       </c>
@@ -1652,28 +1593,28 @@
         <v>1775</v>
       </c>
       <c r="C20">
-        <v>162.692</v>
+        <v>162.69200000000001</v>
       </c>
       <c r="E20">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="F20">
-        <v>0.447</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="G20">
-        <v>0.823</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="H20">
         <v>1645</v>
       </c>
       <c r="I20">
-        <v>161.796</v>
+        <v>161.79599999999999</v>
       </c>
       <c r="K20">
-        <v>0.08699999999999999</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="L20">
-        <v>0.449</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -1682,19 +1623,19 @@
         <v>130</v>
       </c>
       <c r="U20">
-        <v>163.588</v>
+        <v>163.58799999999999</v>
       </c>
       <c r="W20">
-        <v>0.076</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="X20">
-        <v>0.446</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="Y20">
-        <v>0.921</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>0.92100000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1975</v>
       </c>
@@ -1702,28 +1643,28 @@
         <v>1761</v>
       </c>
       <c r="C21">
-        <v>160.413</v>
+        <v>160.41300000000001</v>
       </c>
       <c r="E21">
-        <v>0.082</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="F21">
-        <v>0.352</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="G21">
-        <v>0.732</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="H21">
         <v>1634</v>
       </c>
       <c r="I21">
-        <v>159.338</v>
+        <v>159.33799999999999</v>
       </c>
       <c r="K21">
         <v>0.104</v>
       </c>
       <c r="L21">
-        <v>0.304</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -1741,10 +1682,10 @@
         <v>0.4</v>
       </c>
       <c r="Y21">
-        <v>0.797</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>0.79700000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1976</v>
       </c>
@@ -1755,25 +1696,25 @@
         <v>156.655</v>
       </c>
       <c r="E22">
-        <v>0.077</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="F22">
-        <v>0.289</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="G22">
-        <v>0.6850000000000001</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H22">
         <v>1680</v>
       </c>
       <c r="I22">
-        <v>152.924</v>
+        <v>152.92400000000001</v>
       </c>
       <c r="K22">
-        <v>0.08599999999999999</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="L22">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="N22">
         <v>25</v>
@@ -1782,10 +1723,10 @@
         <v>134</v>
       </c>
       <c r="U22">
-        <v>160.385</v>
+        <v>160.38499999999999</v>
       </c>
       <c r="W22">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="X22">
         <v>0.37</v>
@@ -1794,7 +1735,7 @@
         <v>1.073</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1977</v>
       </c>
@@ -1802,49 +1743,49 @@
         <v>1150.3</v>
       </c>
       <c r="C23">
-        <v>161.469</v>
+        <v>161.46899999999999</v>
       </c>
       <c r="E23">
-        <v>0.083</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="F23">
-        <v>0.402</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="G23">
-        <v>0.645</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="H23">
         <v>1011</v>
       </c>
       <c r="I23">
-        <v>160.83</v>
+        <v>160.83000000000001</v>
       </c>
       <c r="K23">
         <v>0.1</v>
       </c>
       <c r="L23">
-        <v>0.356</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="N23">
         <v>3</v>
       </c>
       <c r="T23">
-        <v>136.3</v>
+        <v>136.30000000000001</v>
       </c>
       <c r="U23">
         <v>162.108</v>
       </c>
       <c r="W23">
-        <v>0.066</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="X23">
-        <v>0.448</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="Y23">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1978</v>
       </c>
@@ -1852,16 +1793,16 @@
         <v>975.2</v>
       </c>
       <c r="C24">
-        <v>163.397</v>
+        <v>163.39699999999999</v>
       </c>
       <c r="E24">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="F24">
-        <v>0.459</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="G24">
-        <v>0.606</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="H24">
         <v>837</v>
@@ -1879,39 +1820,39 @@
         <v>2</v>
       </c>
       <c r="T24">
-        <v>136.2</v>
+        <v>136.19999999999999</v>
       </c>
       <c r="U24">
-        <v>161.062</v>
+        <v>161.06200000000001</v>
       </c>
       <c r="W24">
-        <v>0.083</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="X24">
-        <v>0.417</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="Y24">
         <v>1.002</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1979</v>
       </c>
       <c r="B25">
-        <v>1039.1</v>
+        <v>1039.0999999999999</v>
       </c>
       <c r="C25">
-        <v>159.567</v>
+        <v>159.56700000000001</v>
       </c>
       <c r="E25">
-        <v>0.076</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="F25">
-        <v>0.352</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="G25">
-        <v>0.556</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="H25">
         <v>900.1</v>
@@ -1920,7 +1861,7 @@
         <v>157.512</v>
       </c>
       <c r="K25">
-        <v>0.08400000000000001</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="L25">
         <v>0.26</v>
@@ -1932,10 +1873,10 @@
         <v>134</v>
       </c>
       <c r="U25">
-        <v>161.621</v>
+        <v>161.62100000000001</v>
       </c>
       <c r="W25">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="X25">
         <v>0.443</v>
@@ -1944,12 +1885,12 @@
         <v>1.141</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1980</v>
       </c>
       <c r="B26">
-        <v>976.355</v>
+        <v>976.35500000000002</v>
       </c>
       <c r="C26">
         <v>163.834</v>
@@ -1961,7 +1902,7 @@
         <v>0.43</v>
       </c>
       <c r="G26">
-        <v>0.571</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="H26">
         <v>822</v>
@@ -1970,10 +1911,10 @@
         <v>164.827</v>
       </c>
       <c r="K26">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="L26">
-        <v>0.364</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="N26">
         <v>15.355</v>
@@ -1982,19 +1923,19 @@
         <v>139</v>
       </c>
       <c r="U26">
-        <v>162.842</v>
+        <v>162.84200000000001</v>
       </c>
       <c r="W26">
-        <v>0.07199999999999999</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="X26">
         <v>0.497</v>
       </c>
       <c r="Y26">
-        <v>1.299</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>1.2989999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1981</v>
       </c>
@@ -2002,7 +1943,7 @@
         <v>1240.8</v>
       </c>
       <c r="C27">
-        <v>153.665</v>
+        <v>153.66499999999999</v>
       </c>
       <c r="E27">
         <v>0.113</v>
@@ -2011,7 +1952,7 @@
         <v>0.31</v>
       </c>
       <c r="G27">
-        <v>0.602</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="H27">
         <v>1011</v>
@@ -2023,7 +1964,7 @@
         <v>0.153</v>
       </c>
       <c r="L27">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="N27">
         <v>126.9</v>
@@ -2032,19 +1973,19 @@
         <v>102.9</v>
       </c>
       <c r="U27">
-        <v>161.455</v>
+        <v>161.45500000000001</v>
       </c>
       <c r="W27">
-        <v>0.07199999999999999</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="X27">
-        <v>0.417</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="Y27">
         <v>1.446</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1982</v>
       </c>
@@ -2052,13 +1993,13 @@
         <v>1100.22</v>
       </c>
       <c r="C28">
-        <v>159.418</v>
+        <v>159.41800000000001</v>
       </c>
       <c r="E28">
         <v>0.09</v>
       </c>
       <c r="F28">
-        <v>0.403</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="G28">
         <v>0.626</v>
@@ -2067,34 +2008,34 @@
         <v>990</v>
       </c>
       <c r="I28">
-        <v>158.39</v>
+        <v>158.38999999999999</v>
       </c>
       <c r="K28">
         <v>0.107</v>
       </c>
       <c r="L28">
-        <v>0.415</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="N28">
         <v>32.82</v>
       </c>
       <c r="T28">
-        <v>77.40000000000001</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="U28">
         <v>160.446</v>
       </c>
       <c r="W28">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="X28">
         <v>0.39</v>
       </c>
       <c r="Y28">
-        <v>0.897</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>0.89700000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1983</v>
       </c>
@@ -2102,16 +2043,16 @@
         <v>1779.77</v>
       </c>
       <c r="C29">
-        <v>159.353</v>
+        <v>159.35300000000001</v>
       </c>
       <c r="E29">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="F29">
-        <v>0.381</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="G29">
-        <v>0.656</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="H29">
         <v>1512.47</v>
@@ -2126,7 +2067,7 @@
         <v>0.442</v>
       </c>
       <c r="N29">
-        <v>157.8</v>
+        <v>157.80000000000001</v>
       </c>
       <c r="T29">
         <v>109.5</v>
@@ -2135,16 +2076,16 @@
         <v>158.755</v>
       </c>
       <c r="W29">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="X29">
-        <v>0.321</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="Y29">
-        <v>0.852</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>0.85199999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1984</v>
       </c>
@@ -2152,90 +2093,90 @@
         <v>1213.443</v>
       </c>
       <c r="C30">
-        <v>149.308</v>
+        <v>149.30799999999999</v>
       </c>
       <c r="E30">
         <v>0.12</v>
       </c>
       <c r="F30">
-        <v>0.282</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="G30">
-        <v>0.651</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="H30">
-        <v>1053.59</v>
+        <v>1053.5899999999999</v>
       </c>
       <c r="I30">
         <v>137.262</v>
       </c>
       <c r="K30">
-        <v>0.174</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="L30">
         <v>0.157</v>
       </c>
       <c r="N30">
-        <v>72.35299999999999</v>
+        <v>72.352999999999994</v>
       </c>
       <c r="T30">
         <v>87.5</v>
       </c>
       <c r="U30">
-        <v>161.353</v>
+        <v>161.35300000000001</v>
       </c>
       <c r="W30">
-        <v>0.066</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="X30">
-        <v>0.408</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="Y30">
-        <v>0.844</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>0.84399999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1985</v>
       </c>
       <c r="B31">
-        <v>1729.863</v>
+        <v>1729.8630000000001</v>
       </c>
       <c r="C31">
         <v>160.71</v>
       </c>
       <c r="E31">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="F31">
-        <v>0.396</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="G31">
-        <v>0.661</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="H31">
         <v>1618.57</v>
       </c>
       <c r="N31">
-        <v>44.626</v>
+        <v>44.625999999999998</v>
       </c>
       <c r="T31">
-        <v>66.667</v>
+        <v>66.667000000000002</v>
       </c>
       <c r="U31">
         <v>160.71</v>
       </c>
       <c r="W31">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="X31">
-        <v>0.396</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="Y31">
-        <v>0.696</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>0.69599999999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1986</v>
       </c>
@@ -2243,16 +2184,16 @@
         <v>1688.568</v>
       </c>
       <c r="C32">
-        <v>158.258</v>
+        <v>158.25800000000001</v>
       </c>
       <c r="E32">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="F32">
-        <v>0.355</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="G32">
-        <v>0.614</v>
+        <v>0.61399999999999999</v>
       </c>
       <c r="H32">
         <v>1547.94</v>
@@ -2261,31 +2202,31 @@
         <v>156.214</v>
       </c>
       <c r="K32">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="L32">
         <v>0.313</v>
       </c>
       <c r="N32">
-        <v>83.428</v>
+        <v>83.427999999999997</v>
       </c>
       <c r="T32">
         <v>57.2</v>
       </c>
       <c r="U32">
-        <v>160.302</v>
+        <v>160.30199999999999</v>
       </c>
       <c r="W32">
-        <v>0.063</v>
+        <v>6.3E-2</v>
       </c>
       <c r="X32">
-        <v>0.398</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="Y32">
-        <v>0.985</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>0.98499999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1987</v>
       </c>
@@ -2296,10 +2237,10 @@
         <v>159.738</v>
       </c>
       <c r="E33">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="F33">
-        <v>0.402</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="G33">
         <v>0.622</v>
@@ -2314,10 +2255,10 @@
         <v>0.121</v>
       </c>
       <c r="L33">
-        <v>0.422</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="N33">
-        <v>63.414</v>
+        <v>63.414000000000001</v>
       </c>
       <c r="T33">
         <v>62.6</v>
@@ -2326,45 +2267,45 @@
         <v>160.822</v>
       </c>
       <c r="W33">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="X33">
-        <v>0.382</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="Y33">
         <v>1.032</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1988</v>
       </c>
       <c r="B34">
-        <v>1472.137</v>
+        <v>1472.1369999999999</v>
       </c>
       <c r="C34">
         <v>157.66</v>
       </c>
       <c r="E34">
-        <v>0.08400000000000001</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="F34">
         <v>0.309</v>
       </c>
       <c r="G34">
-        <v>0.581</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="H34">
         <v>1178.78</v>
       </c>
       <c r="I34">
-        <v>153.772</v>
+        <v>153.77199999999999</v>
       </c>
       <c r="K34">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="L34">
-        <v>0.231</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="N34">
         <v>239.357</v>
@@ -2373,51 +2314,51 @@
         <v>54</v>
       </c>
       <c r="U34">
-        <v>161.549</v>
+        <v>161.54900000000001</v>
       </c>
       <c r="W34">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X34">
-        <v>0.387</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="Y34">
-        <v>0.776</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>0.77600000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1989</v>
       </c>
       <c r="B35">
-        <v>1922.727</v>
+        <v>1922.7270000000001</v>
       </c>
       <c r="C35">
-        <v>154.627</v>
+        <v>154.62700000000001</v>
       </c>
       <c r="E35">
-        <v>0.08599999999999999</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="F35">
-        <v>0.237</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="G35">
-        <v>0.545</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H35">
         <v>1799.57</v>
       </c>
       <c r="I35">
-        <v>152.765</v>
+        <v>152.76499999999999</v>
       </c>
       <c r="K35">
         <v>0.11</v>
       </c>
       <c r="L35">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="N35">
-        <v>79.557</v>
+        <v>79.557000000000002</v>
       </c>
       <c r="T35">
         <v>43.6</v>
@@ -2426,16 +2367,16 @@
         <v>156.49</v>
       </c>
       <c r="W35">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="X35">
-        <v>0.277</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="Y35">
-        <v>0.645</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>0.64500000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1990</v>
       </c>
@@ -2443,16 +2384,16 @@
         <v>1738.607</v>
       </c>
       <c r="C36">
-        <v>157.633</v>
+        <v>157.63300000000001</v>
       </c>
       <c r="E36">
-        <v>0.08500000000000001</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="F36">
-        <v>0.384</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="G36">
-        <v>0.514</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="H36">
         <v>1645.37</v>
@@ -2464,42 +2405,42 @@
         <v>0.123</v>
       </c>
       <c r="L36">
-        <v>0.234</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="N36">
-        <v>31.737</v>
+        <v>31.736999999999998</v>
       </c>
       <c r="T36">
         <v>61.5</v>
       </c>
       <c r="U36">
-        <v>164.467</v>
+        <v>164.46700000000001</v>
       </c>
       <c r="W36">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="X36">
-        <v>0.533</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="Y36">
-        <v>0.638</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>0.63800000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1991</v>
       </c>
       <c r="B37">
-        <v>1743.219</v>
+        <v>1743.2190000000001</v>
       </c>
       <c r="C37">
         <v>156.143</v>
       </c>
       <c r="E37">
-        <v>0.093</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="F37">
-        <v>0.257</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2520,96 +2461,96 @@
         <v>21.689</v>
       </c>
       <c r="O37">
-        <v>158.591</v>
+        <v>158.59100000000001</v>
       </c>
       <c r="Q37">
-        <v>0.076</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="R37">
-        <v>0.275</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="S37">
-        <v>0.704</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="T37">
         <v>30.1</v>
       </c>
       <c r="U37">
-        <v>160.736</v>
+        <v>160.73599999999999</v>
       </c>
       <c r="W37">
-        <v>0.07199999999999999</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="X37">
-        <v>0.337</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="Y37">
-        <v>0.718</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>0.71799999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1992</v>
       </c>
       <c r="B38">
-        <v>1557.399</v>
+        <v>1557.3989999999999</v>
       </c>
       <c r="C38">
-        <v>159.647</v>
+        <v>159.64699999999999</v>
       </c>
       <c r="E38">
-        <v>0.075</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F38">
-        <v>0.401</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="G38">
-        <v>0.452</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="H38">
         <v>1500.83</v>
       </c>
       <c r="I38">
-        <v>151.383</v>
+        <v>151.38300000000001</v>
       </c>
       <c r="K38">
         <v>0.113</v>
       </c>
       <c r="L38">
-        <v>0.201</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="N38">
-        <v>25.069</v>
+        <v>25.068999999999999</v>
       </c>
       <c r="O38">
         <v>163.423</v>
       </c>
       <c r="Q38">
-        <v>0.066</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="R38">
-        <v>0.464</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="S38">
-        <v>0.403</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="T38">
         <v>31.5</v>
       </c>
       <c r="U38">
-        <v>164.135</v>
+        <v>164.13499999999999</v>
       </c>
       <c r="W38">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="X38">
-        <v>0.538</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="Y38">
-        <v>0.594</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>0.59399999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1993</v>
       </c>
@@ -2620,7 +2561,7 @@
         <v>161.268</v>
       </c>
       <c r="E39">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="F39">
         <v>0.503</v>
@@ -2638,66 +2579,66 @@
         <v>0.159</v>
       </c>
       <c r="L39">
-        <v>0.342</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="M39">
-        <v>1.378</v>
+        <v>1.3779999999999999</v>
       </c>
       <c r="N39">
-        <v>26.961</v>
+        <v>26.960999999999999</v>
       </c>
       <c r="O39">
-        <v>161.443</v>
+        <v>161.44300000000001</v>
       </c>
       <c r="Q39">
-        <v>0.055</v>
+        <v>5.5E-2</v>
       </c>
       <c r="R39">
-        <v>0.409</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="S39">
-        <v>0.537</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="T39">
         <v>41.7</v>
       </c>
       <c r="U39">
-        <v>170.431</v>
+        <v>170.43100000000001</v>
       </c>
       <c r="W39">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="X39">
-        <v>0.759</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="Y39">
-        <v>0.858</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>0.85799999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1994</v>
       </c>
       <c r="B40">
-        <v>2201.903</v>
+        <v>2201.9029999999998</v>
       </c>
       <c r="C40">
-        <v>161.871</v>
+        <v>161.87100000000001</v>
       </c>
       <c r="E40">
-        <v>0.102</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="F40">
-        <v>0.463</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="G40">
-        <v>0.427</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="H40">
         <v>2128.64</v>
       </c>
       <c r="I40">
-        <v>157.343</v>
+        <v>157.34299999999999</v>
       </c>
       <c r="K40">
         <v>0.154</v>
@@ -2706,19 +2647,19 @@
         <v>0.38</v>
       </c>
       <c r="M40">
-        <v>0.673</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="N40">
-        <v>32.163</v>
+        <v>32.162999999999997</v>
       </c>
       <c r="O40">
         <v>163</v>
       </c>
       <c r="Q40">
-        <v>0.056</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="R40">
-        <v>0.455</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="S40">
         <v>1.988</v>
@@ -2730,16 +2671,16 @@
         <v>165.27</v>
       </c>
       <c r="W40">
-        <v>0.096</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="X40">
-        <v>0.554</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="Y40">
         <v>1.083</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1995</v>
       </c>
@@ -2756,7 +2697,7 @@
         <v>0.315</v>
       </c>
       <c r="G41">
-        <v>0.453</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="H41">
         <v>1841.8</v>
@@ -2765,7 +2706,7 @@
         <v>148.083</v>
       </c>
       <c r="K41">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="L41">
         <v>0.22</v>
@@ -2780,10 +2721,10 @@
         <v>162.035</v>
       </c>
       <c r="Q41">
-        <v>0.063</v>
+        <v>6.3E-2</v>
       </c>
       <c r="R41">
-        <v>0.411</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="S41">
         <v>1.006</v>
@@ -2795,7 +2736,7 @@
         <v>1.093</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1996</v>
       </c>
@@ -2809,37 +2750,37 @@
         <v>0.105</v>
       </c>
       <c r="F42">
-        <v>0.262</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="G42">
-        <v>0.474</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="H42">
         <v>1629.19</v>
       </c>
       <c r="I42">
-        <v>146.835</v>
+        <v>146.83500000000001</v>
       </c>
       <c r="K42">
-        <v>0.149</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="L42">
         <v>0.188</v>
       </c>
       <c r="M42">
-        <v>0.902</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="N42">
-        <v>19.156</v>
+        <v>19.155999999999999</v>
       </c>
       <c r="O42">
         <v>159.928</v>
       </c>
       <c r="Q42">
-        <v>0.061</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="R42">
-        <v>0.337</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="S42">
         <v>0.36</v>
@@ -2848,15 +2789,15 @@
         <v>31</v>
       </c>
       <c r="Y42">
-        <v>1.168</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>1.1679999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1997</v>
       </c>
       <c r="B43">
-        <v>1512.907</v>
+        <v>1512.9069999999999</v>
       </c>
       <c r="C43">
         <v>160.434</v>
@@ -2865,10 +2806,10 @@
         <v>0.113</v>
       </c>
       <c r="F43">
-        <v>0.481</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="G43">
-        <v>0.447</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="H43">
         <v>1482.34</v>
@@ -2880,13 +2821,13 @@
         <v>0.126</v>
       </c>
       <c r="L43">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M43">
-        <v>1.066</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="N43">
-        <v>9.567</v>
+        <v>9.5670000000000002</v>
       </c>
       <c r="S43">
         <v>0.34</v>
@@ -2895,19 +2836,19 @@
         <v>21</v>
       </c>
       <c r="U43">
-        <v>167.545</v>
+        <v>167.54499999999999</v>
       </c>
       <c r="W43">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="X43">
-        <v>0.673</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="Y43">
-        <v>1.063</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>1.0629999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1998</v>
       </c>
@@ -2918,7 +2859,7 @@
         <v>151.339</v>
       </c>
       <c r="E44">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="F44">
         <v>0.378</v>
@@ -2930,49 +2871,49 @@
         <v>1789.23</v>
       </c>
       <c r="I44">
-        <v>151.701</v>
+        <v>151.70099999999999</v>
       </c>
       <c r="K44">
         <v>0.128</v>
       </c>
       <c r="L44">
-        <v>0.286</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="M44">
-        <v>0.886</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="N44">
-        <v>140.963</v>
+        <v>140.96299999999999</v>
       </c>
       <c r="O44">
-        <v>163.722</v>
+        <v>163.72200000000001</v>
       </c>
       <c r="Q44">
-        <v>0.065</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="R44">
         <v>0.504</v>
       </c>
       <c r="S44">
-        <v>0.859</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="T44">
         <v>15.2</v>
       </c>
       <c r="U44">
-        <v>138.594</v>
+        <v>138.59399999999999</v>
       </c>
       <c r="W44">
         <v>0.22</v>
       </c>
       <c r="X44">
-        <v>0.344</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="Y44">
         <v>1.248</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1999</v>
       </c>
@@ -2980,13 +2921,13 @@
         <v>1786.191</v>
       </c>
       <c r="C45">
-        <v>158.616</v>
+        <v>158.61600000000001</v>
       </c>
       <c r="E45">
-        <v>0.116</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="F45">
-        <v>0.397</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="G45">
         <v>0.434</v>
@@ -2995,57 +2936,57 @@
         <v>1731.11</v>
       </c>
       <c r="I45">
-        <v>155.421</v>
+        <v>155.42099999999999</v>
       </c>
       <c r="K45">
         <v>0.17</v>
       </c>
       <c r="L45">
-        <v>0.353</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="M45">
-        <v>1.608</v>
+        <v>1.6080000000000001</v>
       </c>
       <c r="N45">
         <v>40.881</v>
       </c>
       <c r="O45">
-        <v>161.811</v>
+        <v>161.81100000000001</v>
       </c>
       <c r="Q45">
-        <v>0.061</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="R45">
         <v>0.44</v>
       </c>
       <c r="S45">
-        <v>1.495</v>
+        <v>1.4950000000000001</v>
       </c>
       <c r="T45">
         <v>14.2</v>
       </c>
       <c r="Y45">
-        <v>0.731</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>0.73099999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2000</v>
       </c>
       <c r="B46">
-        <v>1552.976</v>
+        <v>1552.9760000000001</v>
       </c>
       <c r="C46">
         <v>159.233</v>
       </c>
       <c r="E46">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="F46">
-        <v>0.397</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="G46">
-        <v>0.449</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="H46">
         <v>1499.37</v>
@@ -3054,25 +2995,25 @@
         <v>155.791</v>
       </c>
       <c r="K46">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="L46">
-        <v>0.332</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="M46">
         <v>1.214</v>
       </c>
       <c r="N46">
-        <v>39.907</v>
+        <v>39.906999999999996</v>
       </c>
       <c r="O46">
-        <v>162.676</v>
+        <v>162.67599999999999</v>
       </c>
       <c r="Q46">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="R46">
-        <v>0.461</v>
+        <v>0.46100000000000002</v>
       </c>
       <c r="S46">
         <v>1.026</v>
@@ -3081,10 +3022,10 @@
         <v>13.699</v>
       </c>
       <c r="Y46">
-        <v>0.775</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>0.77500000000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2001</v>
       </c>
@@ -3092,55 +3033,55 @@
         <v>1089.425</v>
       </c>
       <c r="C47">
-        <v>157.031</v>
+        <v>157.03100000000001</v>
       </c>
       <c r="E47">
         <v>0.105</v>
       </c>
       <c r="F47">
-        <v>0.389</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="G47">
-        <v>0.411</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="H47">
         <v>1036.23</v>
       </c>
       <c r="I47">
-        <v>149.992</v>
+        <v>149.99199999999999</v>
       </c>
       <c r="K47">
-        <v>0.141</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="L47">
         <v>0.216</v>
       </c>
       <c r="M47">
-        <v>0.492</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="N47">
-        <v>35.676</v>
+        <v>35.676000000000002</v>
       </c>
       <c r="O47">
         <v>164.07</v>
       </c>
       <c r="Q47">
-        <v>0.06900000000000001</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="R47">
-        <v>0.5629999999999999</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="S47">
-        <v>0.636</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="T47">
-        <v>17.518</v>
+        <v>17.518000000000001</v>
       </c>
       <c r="Y47">
-        <v>0.924</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>0.92400000000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2002</v>
       </c>
@@ -3148,46 +3089,46 @@
         <v>1018.957</v>
       </c>
       <c r="C48">
-        <v>162.609</v>
+        <v>162.60900000000001</v>
       </c>
       <c r="E48">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="F48">
-        <v>0.572</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="G48">
         <v>0.372</v>
       </c>
       <c r="H48">
-        <v>907.874</v>
+        <v>907.87400000000002</v>
       </c>
       <c r="I48">
-        <v>151.235</v>
+        <v>151.23500000000001</v>
       </c>
       <c r="K48">
-        <v>0.103</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="L48">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="M48">
-        <v>1.001</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="N48">
-        <v>93.39400000000001</v>
+        <v>93.394000000000005</v>
       </c>
       <c r="O48">
         <v>163.95</v>
       </c>
       <c r="Q48">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="R48">
         <v>0.52</v>
       </c>
       <c r="S48">
-        <v>0.894</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="T48">
         <v>17.689</v>
@@ -3196,7 +3137,7 @@
         <v>172.642</v>
       </c>
       <c r="W48">
-        <v>0.028</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="X48">
         <v>1</v>
@@ -3205,21 +3146,21 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2003</v>
       </c>
       <c r="B49">
-        <v>850.075</v>
+        <v>850.07500000000005</v>
       </c>
       <c r="C49">
         <v>159.614</v>
       </c>
       <c r="E49">
-        <v>0.117</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="F49">
-        <v>0.452</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="G49">
         <v>0.34</v>
@@ -3228,184 +3169,184 @@
         <v>815.601</v>
       </c>
       <c r="I49">
-        <v>153.252</v>
+        <v>153.25200000000001</v>
       </c>
       <c r="K49">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="L49">
-        <v>0.357</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="M49">
-        <v>0.5580000000000001</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="N49">
-        <v>20.655</v>
+        <v>20.655000000000001</v>
       </c>
       <c r="O49">
-        <v>165.975</v>
+        <v>165.97499999999999</v>
       </c>
       <c r="Q49">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="R49">
-        <v>0.547</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="S49">
-        <v>0.974</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="T49">
-        <v>13.819</v>
+        <v>13.819000000000001</v>
       </c>
       <c r="Y49">
-        <v>0.796</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>0.79600000000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2004</v>
       </c>
       <c r="B50">
-        <v>848.466</v>
+        <v>848.46600000000001</v>
       </c>
       <c r="C50">
         <v>159.279</v>
       </c>
       <c r="E50">
-        <v>0.091</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="F50">
-        <v>0.396</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="G50">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="H50">
-        <v>812.331</v>
+        <v>812.33100000000002</v>
       </c>
       <c r="I50">
-        <v>158.694</v>
+        <v>158.69399999999999</v>
       </c>
       <c r="K50">
         <v>0.12</v>
       </c>
       <c r="L50">
-        <v>0.423</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="M50">
-        <v>0.968</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="N50">
         <v>22.186</v>
       </c>
       <c r="O50">
-        <v>159.865</v>
+        <v>159.86500000000001</v>
       </c>
       <c r="Q50">
-        <v>0.063</v>
+        <v>6.3E-2</v>
       </c>
       <c r="R50">
-        <v>0.368</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="S50">
-        <v>1.463</v>
+        <v>1.4630000000000001</v>
       </c>
       <c r="T50">
         <v>13.949</v>
       </c>
       <c r="Y50">
-        <v>0.854</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>0.85399999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2005</v>
       </c>
       <c r="B51">
-        <v>769.808</v>
+        <v>769.80799999999999</v>
       </c>
       <c r="C51">
-        <v>159.116</v>
+        <v>159.11600000000001</v>
       </c>
       <c r="E51">
         <v>0.113</v>
       </c>
       <c r="F51">
-        <v>0.382</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="G51">
-        <v>0.334</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="H51">
-        <v>741.591</v>
+        <v>741.59100000000001</v>
       </c>
       <c r="I51">
         <v>155.876</v>
       </c>
       <c r="K51">
-        <v>0.164</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="L51">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="M51">
-        <v>1.247</v>
+        <v>1.2470000000000001</v>
       </c>
       <c r="N51">
-        <v>16.179</v>
+        <v>16.178999999999998</v>
       </c>
       <c r="O51">
-        <v>162.355</v>
+        <v>162.35499999999999</v>
       </c>
       <c r="Q51">
-        <v>0.061</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="R51">
-        <v>0.426</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="S51">
-        <v>1.481</v>
+        <v>1.4810000000000001</v>
       </c>
       <c r="T51">
         <v>12.038</v>
       </c>
       <c r="Y51">
-        <v>0.931</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>0.93100000000000005</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2006</v>
       </c>
       <c r="B52">
-        <v>618.643</v>
+        <v>618.64300000000003</v>
       </c>
       <c r="C52">
-        <v>162.546</v>
+        <v>162.54599999999999</v>
       </c>
       <c r="E52">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="F52">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="G52">
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="H52">
-        <v>580.268</v>
+        <v>580.26800000000003</v>
       </c>
       <c r="I52">
         <v>153.648</v>
       </c>
       <c r="K52">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="L52">
-        <v>0.323</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="M52">
-        <v>0.804</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="N52">
         <v>25.994</v>
@@ -3414,10 +3355,10 @@
         <v>161.971</v>
       </c>
       <c r="Q52">
-        <v>0.066</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="R52">
-        <v>0.454</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="S52">
         <v>1.419</v>
@@ -3429,27 +3370,27 @@
         <v>172.018</v>
       </c>
       <c r="W52">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.166</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>1.1659999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2007</v>
       </c>
       <c r="B53">
-        <v>766.7569999999999</v>
+        <v>766.75699999999995</v>
       </c>
       <c r="C53">
-        <v>159.616</v>
+        <v>159.61600000000001</v>
       </c>
       <c r="E53">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="F53">
         <v>0.43</v>
@@ -3458,34 +3399,34 @@
         <v>0.34</v>
       </c>
       <c r="H53">
-        <v>719.083</v>
+        <v>719.08299999999997</v>
       </c>
       <c r="I53">
-        <v>156.89</v>
+        <v>156.88999999999999</v>
       </c>
       <c r="K53">
-        <v>0.143</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="L53">
         <v>0.41</v>
       </c>
       <c r="M53">
-        <v>0.607</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="N53">
-        <v>37.392</v>
+        <v>37.392000000000003</v>
       </c>
       <c r="O53">
-        <v>162.343</v>
+        <v>162.34299999999999</v>
       </c>
       <c r="Q53">
-        <v>0.054</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="R53">
         <v>0.45</v>
       </c>
       <c r="S53">
-        <v>1.624</v>
+        <v>1.6240000000000001</v>
       </c>
       <c r="T53">
         <v>10.282</v>
@@ -3494,95 +3435,95 @@
         <v>1.085</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2008</v>
       </c>
       <c r="B54">
-        <v>737.9109999999999</v>
+        <v>737.91099999999994</v>
       </c>
       <c r="C54">
         <v>164.89</v>
       </c>
       <c r="E54">
-        <v>0.076</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="F54">
-        <v>0.619</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="G54">
-        <v>0.345</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="H54">
-        <v>687.6609999999999</v>
+        <v>687.66099999999994</v>
       </c>
       <c r="I54">
-        <v>154.633</v>
+        <v>154.63300000000001</v>
       </c>
       <c r="K54">
         <v>0.127</v>
       </c>
       <c r="L54">
-        <v>0.283</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="M54">
-        <v>0.591</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="N54">
-        <v>38.271</v>
+        <v>38.271000000000001</v>
       </c>
       <c r="O54">
-        <v>164.296</v>
+        <v>164.29599999999999</v>
       </c>
       <c r="Q54">
-        <v>0.058</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="R54">
-        <v>0.574</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="S54">
         <v>1.165</v>
       </c>
       <c r="T54">
-        <v>11.979</v>
+        <v>11.978999999999999</v>
       </c>
       <c r="U54">
-        <v>175.741</v>
+        <v>175.74100000000001</v>
       </c>
       <c r="W54">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="X54">
         <v>1</v>
       </c>
       <c r="Y54">
-        <v>0.848</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>0.84799999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2009</v>
       </c>
       <c r="B55">
-        <v>788.026</v>
+        <v>788.02599999999995</v>
       </c>
       <c r="C55">
-        <v>163.389</v>
+        <v>163.38900000000001</v>
       </c>
       <c r="E55">
-        <v>0.066</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="F55">
-        <v>0.555</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="G55">
-        <v>0.361</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="H55">
-        <v>726.162</v>
+        <v>726.16200000000003</v>
       </c>
       <c r="I55">
-        <v>154.076</v>
+        <v>154.07599999999999</v>
       </c>
       <c r="K55">
         <v>0.106</v>
@@ -3591,122 +3532,122 @@
         <v>0.183</v>
       </c>
       <c r="M55">
-        <v>1.017</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="N55">
-        <v>47.657</v>
+        <v>47.656999999999996</v>
       </c>
       <c r="O55">
         <v>162.59</v>
       </c>
       <c r="Q55">
-        <v>0.059</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="R55">
-        <v>0.481</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="S55">
-        <v>0.992</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="T55">
-        <v>14.207</v>
+        <v>14.207000000000001</v>
       </c>
       <c r="U55">
         <v>173.5</v>
       </c>
       <c r="W55">
-        <v>0.033</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="X55">
         <v>1</v>
       </c>
       <c r="Y55">
-        <v>0.634</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>0.63400000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2010</v>
       </c>
       <c r="B56">
-        <v>531.376</v>
+        <v>531.37599999999998</v>
       </c>
       <c r="C56">
         <v>164.364</v>
       </c>
       <c r="E56">
-        <v>0.074</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="F56">
         <v>0.59</v>
       </c>
       <c r="G56">
-        <v>0.362</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="H56">
-        <v>494.946</v>
+        <v>494.94600000000003</v>
       </c>
       <c r="I56">
         <v>153.065</v>
       </c>
       <c r="K56">
-        <v>0.102</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="L56">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="M56">
-        <v>0.656</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="N56">
-        <v>21.795</v>
+        <v>21.795000000000002</v>
       </c>
       <c r="S56">
-        <v>0.636</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="T56">
         <v>14.635</v>
       </c>
       <c r="U56">
-        <v>175.663</v>
+        <v>175.66300000000001</v>
       </c>
       <c r="W56">
-        <v>0.046</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="X56">
         <v>1</v>
       </c>
       <c r="Y56">
-        <v>0.948</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>0.94799999999999995</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2011</v>
       </c>
       <c r="B57">
-        <v>550.044</v>
+        <v>550.04399999999998</v>
       </c>
       <c r="C57">
         <v>163.739</v>
       </c>
       <c r="E57">
-        <v>0.07099999999999999</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="F57">
-        <v>0.581</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="G57">
-        <v>0.369</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="H57">
         <v>500.904</v>
       </c>
       <c r="I57">
-        <v>152.871</v>
+        <v>152.87100000000001</v>
       </c>
       <c r="K57">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="L57">
         <v>0.184</v>
@@ -3715,33 +3656,33 @@
         <v>1.64</v>
       </c>
       <c r="N57">
-        <v>9.496</v>
+        <v>9.4960000000000004</v>
       </c>
       <c r="T57">
-        <v>39.644</v>
+        <v>39.643999999999998</v>
       </c>
       <c r="U57">
         <v>174.607</v>
       </c>
       <c r="W57">
-        <v>0.043</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="X57">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="Y57">
         <v>1.071</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2012</v>
       </c>
       <c r="B58">
-        <v>489.068</v>
+        <v>489.06799999999998</v>
       </c>
       <c r="C58">
-        <v>150.091</v>
+        <v>150.09100000000001</v>
       </c>
       <c r="E58">
         <v>0.09</v>
@@ -3753,10 +3694,10 @@
         <v>0.371</v>
       </c>
       <c r="H58">
-        <v>461.176</v>
+        <v>461.17599999999999</v>
       </c>
       <c r="I58">
-        <v>150.091</v>
+        <v>150.09100000000001</v>
       </c>
       <c r="K58">
         <v>0.09</v>
@@ -3768,48 +3709,48 @@
         <v>1.526</v>
       </c>
       <c r="N58">
-        <v>26.374</v>
+        <v>26.373999999999999</v>
       </c>
       <c r="T58">
-        <v>1.519</v>
+        <v>1.5189999999999999</v>
       </c>
       <c r="Y58">
-        <v>1.009</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>1.0089999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2013</v>
       </c>
       <c r="B59">
-        <v>660.659</v>
+        <v>660.65899999999999</v>
       </c>
       <c r="C59">
         <v>152.04</v>
       </c>
       <c r="E59">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="F59">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="G59">
-        <v>0.399</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="H59">
-        <v>530.397</v>
+        <v>530.39700000000005</v>
       </c>
       <c r="I59">
         <v>152.04</v>
       </c>
       <c r="K59">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="L59">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="M59">
-        <v>0.919</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="N59">
         <v>126.292</v>
@@ -3818,10 +3759,10 @@
         <v>3.97</v>
       </c>
       <c r="Y59">
-        <v>1.311</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>1.3109999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2014</v>
       </c>
@@ -3829,40 +3770,40 @@
         <v>474.85</v>
       </c>
       <c r="C60">
-        <v>156.479</v>
+        <v>156.47900000000001</v>
       </c>
       <c r="E60">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="F60">
         <v>0.443</v>
       </c>
       <c r="G60">
-        <v>0.422</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="H60">
-        <v>449.931</v>
+        <v>449.93099999999998</v>
       </c>
       <c r="I60">
         <v>152.142</v>
       </c>
       <c r="K60">
-        <v>0.119</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="L60">
-        <v>0.132</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="M60">
-        <v>0.984</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="N60">
-        <v>22.548</v>
+        <v>22.547999999999998</v>
       </c>
       <c r="O60">
         <v>160.816</v>
       </c>
       <c r="Q60">
-        <v>0.275</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="R60">
         <v>0.755</v>
@@ -3871,10 +3812,10 @@
         <v>2.371</v>
       </c>
       <c r="Y60">
-        <v>0.9419999999999999</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>0.94199999999999995</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2015</v>
       </c>
@@ -3882,119 +3823,119 @@
         <v>505.767</v>
       </c>
       <c r="C61">
-        <v>152.027</v>
+        <v>152.02699999999999</v>
       </c>
       <c r="E61">
-        <v>0.08400000000000001</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="F61">
         <v>0.129</v>
       </c>
       <c r="G61">
-        <v>0.448</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="H61">
-        <v>485.978</v>
+        <v>485.97800000000001</v>
       </c>
       <c r="I61">
-        <v>152.027</v>
+        <v>152.02699999999999</v>
       </c>
       <c r="K61">
-        <v>0.08400000000000001</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="L61">
         <v>0.129</v>
       </c>
       <c r="M61">
-        <v>1.033</v>
+        <v>1.0329999999999999</v>
       </c>
       <c r="N61">
         <v>16.544</v>
       </c>
       <c r="T61">
-        <v>3.244</v>
+        <v>3.2440000000000002</v>
       </c>
       <c r="Y61">
-        <v>0.802</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>0.80200000000000005</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2016</v>
       </c>
       <c r="B62">
-        <v>485.563</v>
+        <v>485.56299999999999</v>
       </c>
       <c r="C62">
-        <v>153.373</v>
+        <v>153.37299999999999</v>
       </c>
       <c r="E62">
-        <v>0.08500000000000001</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="F62">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="G62">
-        <v>0.454</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="H62">
         <v>464.178</v>
       </c>
       <c r="I62">
-        <v>153.373</v>
+        <v>153.37299999999999</v>
       </c>
       <c r="K62">
-        <v>0.08500000000000001</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="L62">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="M62">
-        <v>0.984</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="N62">
-        <v>19.437</v>
+        <v>19.437000000000001</v>
       </c>
       <c r="T62">
         <v>1.948</v>
       </c>
       <c r="Y62">
-        <v>0.735</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>0.73499999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2017</v>
       </c>
       <c r="B63">
-        <v>493.609</v>
+        <v>493.60899999999998</v>
       </c>
       <c r="C63">
-        <v>166.498</v>
+        <v>166.49799999999999</v>
       </c>
       <c r="E63">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="F63">
-        <v>0.619</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="G63">
-        <v>0.481</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="H63">
-        <v>467.357</v>
+        <v>467.35700000000003</v>
       </c>
       <c r="I63">
-        <v>154.056</v>
+        <v>154.05600000000001</v>
       </c>
       <c r="K63">
         <v>0.09</v>
       </c>
       <c r="L63">
-        <v>0.176</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="M63">
-        <v>0.902</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="N63">
         <v>20.259</v>
@@ -4003,25 +3944,25 @@
         <v>172.685</v>
       </c>
       <c r="Q63">
-        <v>0.103</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="R63">
-        <v>0.704</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="T63">
-        <v>5.993</v>
+        <v>5.9930000000000003</v>
       </c>
       <c r="U63">
-        <v>172.753</v>
+        <v>172.75299999999999</v>
       </c>
       <c r="W63">
-        <v>0.043</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="X63">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="Y63">
-        <v>0.673</v>
+        <v>0.67300000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Indicator_4/Real_data/White_Marlin_Atl.xlsx
+++ b/Indicator_4/Real_data/White_Marlin_Atl.xlsx
@@ -1,294 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4EA0BC-9BE4-4CD0-821B-D081DCF340F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>White_Marlin_Atl</t>
-  </si>
-  <si>
-    <t>E.g. 'Swordfish_Natl'</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>max_age</t>
-  </si>
-  <si>
-    <t>14.979</t>
-  </si>
-  <si>
-    <t>Age to 5% natural survival</t>
-  </si>
-  <si>
-    <t>Life history</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>von Bertalannfy K</t>
-  </si>
-  <si>
-    <t>Linf</t>
-  </si>
-  <si>
-    <t>0.932</t>
-  </si>
-  <si>
-    <t>von Bertalannfy L-infinity (asymptotic length)</t>
-  </si>
-  <si>
-    <t>L50_Linf</t>
-  </si>
-  <si>
-    <t>172.1</t>
-  </si>
-  <si>
-    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-  </si>
-  <si>
-    <t>Total_L5_L50</t>
-  </si>
-  <si>
-    <t>0.673</t>
-  </si>
-  <si>
-    <t>Length at 5% selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Fleet selectivity</t>
-  </si>
-  <si>
-    <t>All fleets combined</t>
-  </si>
-  <si>
-    <t>Total_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.989</t>
-  </si>
-  <si>
-    <t>Length at full selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Total_VML</t>
-  </si>
-  <si>
-    <t>0.962</t>
-  </si>
-  <si>
-    <t>Selectivity of maximum length class</t>
-  </si>
-  <si>
-    <t>Fleet_1_L5_L50</t>
-  </si>
-  <si>
-    <t>0.671</t>
-  </si>
-  <si>
-    <t>Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet_1_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.984</t>
-  </si>
-  <si>
-    <t>Fleet_1_VML</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Fleet_2_L5_L50</t>
-  </si>
-  <si>
-    <t>0.892</t>
-  </si>
-  <si>
-    <t>Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_2_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.01</t>
-  </si>
-  <si>
-    <t>Fleet_2_VML</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>Fleet_3_L5_L50</t>
-  </si>
-  <si>
-    <t>0.699</t>
-  </si>
-  <si>
-    <t>Fleet 3</t>
-  </si>
-  <si>
-    <t>Fleet_3_LFS_L50</t>
-  </si>
-  <si>
-    <t>Fleet_3_VML</t>
-  </si>
-  <si>
-    <t>Fleet_1_CF</t>
-  </si>
-  <si>
-    <t>0.939</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet catch scale</t>
-  </si>
-  <si>
-    <t>Fleet_2_CF</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_3_CF</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 3</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Total_catch</t>
-  </si>
-  <si>
-    <t>Total_mean_len</t>
-  </si>
-  <si>
-    <t>Total_mean_age</t>
-  </si>
-  <si>
-    <t>Total_CV_len</t>
-  </si>
-  <si>
-    <t>Total_frac_mat</t>
-  </si>
-  <si>
-    <t>Total_Index</t>
-  </si>
-  <si>
-    <t>Fleet_1_catch</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_1_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_1_Index</t>
-  </si>
-  <si>
-    <t>Fleet_2_catch</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_2_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_2_Index</t>
-  </si>
-  <si>
-    <t>Fleet_3_catch</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_3_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_3_Index</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -388,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -422,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -457,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -633,365 +351,575 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>White_Marlin_Atl</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E.g. 'Swordfish_Natl'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_age</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14.979</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age to 5% natural survival</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>von Bertalannfy K</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.932</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>von Bertalannfy L-infinity (asymptotic length)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L50_Linf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>172.1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total_L5_L50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.673</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.989</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total_VML</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.962</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fleet_1_L5_L50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.671</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fleet_1_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.984</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fleet_1_VML</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fleet_2_L5_L50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.892</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fleet_2_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fleet_2_VML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.085</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet_3_L5_L50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.699</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fleet_3_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.984</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fleet_3_VML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fleet_1_CF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.939</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fleet_2_CF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.022</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fleet_3_CF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.039</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1000,88 +928,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y63"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_catch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_len</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total_CV_len</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total_frac_mat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Index</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_len</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_age</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_CV_len</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_frac_mat</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_Index</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_catch</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_len</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_age</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_CV_len</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_frac_mat</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_Index</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_catch</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_len</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_age</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_CV_len</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_frac_mat</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1956</v>
       </c>
@@ -1089,7 +1067,7 @@
         <v>19</v>
       </c>
       <c r="G2">
-        <v>3.0129999999999999</v>
+        <v>3.013</v>
       </c>
       <c r="H2">
         <v>19</v>
@@ -1101,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>1957</v>
       </c>
@@ -1109,7 +1087,7 @@
         <v>160</v>
       </c>
       <c r="G3">
-        <v>3.0129999999999999</v>
+        <v>3.013</v>
       </c>
       <c r="H3">
         <v>160</v>
@@ -1121,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>1958</v>
       </c>
@@ -1129,7 +1107,7 @@
         <v>161</v>
       </c>
       <c r="G4">
-        <v>3.0129999999999999</v>
+        <v>3.013</v>
       </c>
       <c r="H4">
         <v>161</v>
@@ -1141,7 +1119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5">
         <v>1959</v>
       </c>
@@ -1149,7 +1127,7 @@
         <v>112</v>
       </c>
       <c r="G5">
-        <v>3.0110000000000001</v>
+        <v>3.011</v>
       </c>
       <c r="H5">
         <v>112</v>
@@ -1161,10 +1139,10 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0.24199999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.242</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>1960</v>
       </c>
@@ -1172,7 +1150,7 @@
         <v>313</v>
       </c>
       <c r="G6">
-        <v>2.9910000000000001</v>
+        <v>2.991</v>
       </c>
       <c r="H6">
         <v>253</v>
@@ -1184,10 +1162,10 @@
         <v>60</v>
       </c>
       <c r="Y6">
-        <v>0.40799999999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.408</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>1961</v>
       </c>
@@ -1210,7 +1188,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>1962</v>
       </c>
@@ -1218,7 +1196,7 @@
         <v>2064</v>
       </c>
       <c r="G8">
-        <v>2.9620000000000002</v>
+        <v>2.962</v>
       </c>
       <c r="H8">
         <v>1985</v>
@@ -1230,10 +1208,10 @@
         <v>79</v>
       </c>
       <c r="Y8">
-        <v>2.0179999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2.018</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>1963</v>
       </c>
@@ -1241,7 +1219,7 @@
         <v>2614</v>
       </c>
       <c r="G9">
-        <v>2.9279999999999999</v>
+        <v>2.928</v>
       </c>
       <c r="H9">
         <v>2548</v>
@@ -1256,7 +1234,7 @@
         <v>1.921</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>1964</v>
       </c>
@@ -1264,7 +1242,7 @@
         <v>3735</v>
       </c>
       <c r="G10">
-        <v>2.8319999999999999</v>
+        <v>2.832</v>
       </c>
       <c r="H10">
         <v>3661</v>
@@ -1276,10 +1254,10 @@
         <v>74</v>
       </c>
       <c r="Y10">
-        <v>1.5149999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.515</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>1965</v>
       </c>
@@ -1287,7 +1265,7 @@
         <v>4906</v>
       </c>
       <c r="G11">
-        <v>2.5920000000000001</v>
+        <v>2.592</v>
       </c>
       <c r="H11">
         <v>4827</v>
@@ -1299,10 +1277,10 @@
         <v>79</v>
       </c>
       <c r="Y11">
-        <v>1.3620000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.362</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>1966</v>
       </c>
@@ -1310,7 +1288,7 @@
         <v>3513</v>
       </c>
       <c r="G12">
-        <v>2.3079999999999998</v>
+        <v>2.308</v>
       </c>
       <c r="H12">
         <v>3425</v>
@@ -1322,10 +1300,10 @@
         <v>88</v>
       </c>
       <c r="Y12">
-        <v>1.6160000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.616</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>1967</v>
       </c>
@@ -1348,7 +1326,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14">
         <v>1968</v>
       </c>
@@ -1356,7 +1334,7 @@
         <v>2049</v>
       </c>
       <c r="G14">
-        <v>1.4410000000000001</v>
+        <v>1.441</v>
       </c>
       <c r="H14">
         <v>1949</v>
@@ -1368,10 +1346,10 @@
         <v>100</v>
       </c>
       <c r="Y14">
-        <v>1.5820000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.582</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>1969</v>
       </c>
@@ -1379,7 +1357,7 @@
         <v>2272</v>
       </c>
       <c r="G15">
-        <v>1.1739999999999999</v>
+        <v>1.174</v>
       </c>
       <c r="H15">
         <v>2171</v>
@@ -1391,10 +1369,10 @@
         <v>101</v>
       </c>
       <c r="Y15">
-        <v>1.4319999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.432</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>1970</v>
       </c>
@@ -1402,13 +1380,13 @@
         <v>2147</v>
       </c>
       <c r="C16">
-        <v>167.43299999999999</v>
+        <v>167.433</v>
       </c>
       <c r="E16">
-        <v>0.16800000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="F16">
-        <v>0.47299999999999998</v>
+        <v>0.473</v>
       </c>
       <c r="G16">
         <v>1.161</v>
@@ -1417,13 +1395,13 @@
         <v>2027</v>
       </c>
       <c r="I16">
-        <v>167.43299999999999</v>
+        <v>167.433</v>
       </c>
       <c r="K16">
-        <v>0.16800000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="L16">
-        <v>0.47299999999999998</v>
+        <v>0.473</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1432,10 +1410,10 @@
         <v>120</v>
       </c>
       <c r="Y16">
-        <v>1.0269999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.027</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>1971</v>
       </c>
@@ -1443,7 +1421,7 @@
         <v>2266</v>
       </c>
       <c r="C17">
-        <v>162.44200000000001</v>
+        <v>162.442</v>
       </c>
       <c r="E17">
         <v>0.105</v>
@@ -1452,19 +1430,19 @@
         <v>0.435</v>
       </c>
       <c r="G17">
-        <v>1.0860000000000001</v>
+        <v>1.086</v>
       </c>
       <c r="H17">
         <v>2153</v>
       </c>
       <c r="I17">
-        <v>161.15799999999999</v>
+        <v>161.158</v>
       </c>
       <c r="K17">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="L17">
-        <v>0.36599999999999999</v>
+        <v>0.366</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1476,16 +1454,16 @@
         <v>163.726</v>
       </c>
       <c r="W17">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="X17">
         <v>0.503</v>
       </c>
       <c r="Y17">
-        <v>1.0289999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.029</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>1972</v>
       </c>
@@ -1493,28 +1471,28 @@
         <v>2289</v>
       </c>
       <c r="C18">
-        <v>161.46100000000001</v>
+        <v>161.461</v>
       </c>
       <c r="E18">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="F18">
-        <v>0.40400000000000003</v>
+        <v>0.404</v>
       </c>
       <c r="G18">
-        <v>0.99099999999999999</v>
+        <v>0.991</v>
       </c>
       <c r="H18">
         <v>2171</v>
       </c>
       <c r="I18">
-        <v>158.53800000000001</v>
+        <v>158.538</v>
       </c>
       <c r="K18">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L18">
-        <v>0.23400000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -1523,19 +1501,19 @@
         <v>118</v>
       </c>
       <c r="U18">
-        <v>164.38399999999999</v>
+        <v>164.384</v>
       </c>
       <c r="W18">
-        <v>6.7000000000000004E-2</v>
+        <v>0.067</v>
       </c>
       <c r="X18">
-        <v>0.57399999999999995</v>
+        <v>0.574</v>
       </c>
       <c r="Y18">
-        <v>0.84099999999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.841</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>1973</v>
       </c>
@@ -1543,16 +1521,16 @@
         <v>1868</v>
       </c>
       <c r="C19">
-        <v>158.27799999999999</v>
+        <v>158.278</v>
       </c>
       <c r="E19">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="F19">
-        <v>0.36899999999999999</v>
+        <v>0.369</v>
       </c>
       <c r="G19">
-        <v>0.91200000000000003</v>
+        <v>0.912</v>
       </c>
       <c r="H19">
         <v>1750</v>
@@ -1561,10 +1539,10 @@
         <v>152.297</v>
       </c>
       <c r="K19">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="L19">
-        <v>0.21099999999999999</v>
+        <v>0.211</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -1573,19 +1551,19 @@
         <v>118</v>
       </c>
       <c r="U19">
-        <v>164.25899999999999</v>
+        <v>164.259</v>
       </c>
       <c r="W19">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="X19">
-        <v>0.52700000000000002</v>
+        <v>0.527</v>
       </c>
       <c r="Y19">
         <v>0.998</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20">
         <v>1974</v>
       </c>
@@ -1593,28 +1571,28 @@
         <v>1775</v>
       </c>
       <c r="C20">
-        <v>162.69200000000001</v>
+        <v>162.692</v>
       </c>
       <c r="E20">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="F20">
-        <v>0.44700000000000001</v>
+        <v>0.447</v>
       </c>
       <c r="G20">
-        <v>0.82299999999999995</v>
+        <v>0.823</v>
       </c>
       <c r="H20">
         <v>1645</v>
       </c>
       <c r="I20">
-        <v>161.79599999999999</v>
+        <v>161.796</v>
       </c>
       <c r="K20">
-        <v>8.6999999999999994E-2</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L20">
-        <v>0.44900000000000001</v>
+        <v>0.449</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -1623,19 +1601,19 @@
         <v>130</v>
       </c>
       <c r="U20">
-        <v>163.58799999999999</v>
+        <v>163.588</v>
       </c>
       <c r="W20">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="X20">
-        <v>0.44600000000000001</v>
+        <v>0.446</v>
       </c>
       <c r="Y20">
-        <v>0.92100000000000004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.921</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>1975</v>
       </c>
@@ -1643,28 +1621,28 @@
         <v>1761</v>
       </c>
       <c r="C21">
-        <v>160.41300000000001</v>
+        <v>160.413</v>
       </c>
       <c r="E21">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="F21">
-        <v>0.35199999999999998</v>
+        <v>0.352</v>
       </c>
       <c r="G21">
-        <v>0.73199999999999998</v>
+        <v>0.732</v>
       </c>
       <c r="H21">
         <v>1634</v>
       </c>
       <c r="I21">
-        <v>159.33799999999999</v>
+        <v>159.338</v>
       </c>
       <c r="K21">
         <v>0.104</v>
       </c>
       <c r="L21">
-        <v>0.30399999999999999</v>
+        <v>0.304</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -1682,10 +1660,10 @@
         <v>0.4</v>
       </c>
       <c r="Y21">
-        <v>0.79700000000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.797</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>1976</v>
       </c>
@@ -1696,25 +1674,25 @@
         <v>156.655</v>
       </c>
       <c r="E22">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="F22">
-        <v>0.28899999999999998</v>
+        <v>0.289</v>
       </c>
       <c r="G22">
-        <v>0.68500000000000005</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H22">
         <v>1680</v>
       </c>
       <c r="I22">
-        <v>152.92400000000001</v>
+        <v>152.924</v>
       </c>
       <c r="K22">
-        <v>8.5999999999999993E-2</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L22">
-        <v>0.20799999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="N22">
         <v>25</v>
@@ -1723,10 +1701,10 @@
         <v>134</v>
       </c>
       <c r="U22">
-        <v>160.38499999999999</v>
+        <v>160.385</v>
       </c>
       <c r="W22">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="X22">
         <v>0.37</v>
@@ -1735,7 +1713,7 @@
         <v>1.073</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23">
         <v>1977</v>
       </c>
@@ -1743,49 +1721,49 @@
         <v>1150.3</v>
       </c>
       <c r="C23">
-        <v>161.46899999999999</v>
+        <v>161.469</v>
       </c>
       <c r="E23">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="F23">
-        <v>0.40200000000000002</v>
+        <v>0.402</v>
       </c>
       <c r="G23">
-        <v>0.64500000000000002</v>
+        <v>0.645</v>
       </c>
       <c r="H23">
         <v>1011</v>
       </c>
       <c r="I23">
-        <v>160.83000000000001</v>
+        <v>160.83</v>
       </c>
       <c r="K23">
         <v>0.1</v>
       </c>
       <c r="L23">
-        <v>0.35599999999999998</v>
+        <v>0.356</v>
       </c>
       <c r="N23">
         <v>3</v>
       </c>
       <c r="T23">
-        <v>136.30000000000001</v>
+        <v>136.3</v>
       </c>
       <c r="U23">
         <v>162.108</v>
       </c>
       <c r="W23">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="X23">
-        <v>0.44800000000000001</v>
+        <v>0.448</v>
       </c>
       <c r="Y23">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>1978</v>
       </c>
@@ -1793,16 +1771,16 @@
         <v>975.2</v>
       </c>
       <c r="C24">
-        <v>163.39699999999999</v>
+        <v>163.397</v>
       </c>
       <c r="E24">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="F24">
-        <v>0.45900000000000002</v>
+        <v>0.459</v>
       </c>
       <c r="G24">
-        <v>0.60599999999999998</v>
+        <v>0.606</v>
       </c>
       <c r="H24">
         <v>837</v>
@@ -1820,39 +1798,39 @@
         <v>2</v>
       </c>
       <c r="T24">
-        <v>136.19999999999999</v>
+        <v>136.2</v>
       </c>
       <c r="U24">
-        <v>161.06200000000001</v>
+        <v>161.062</v>
       </c>
       <c r="W24">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="X24">
-        <v>0.41699999999999998</v>
+        <v>0.417</v>
       </c>
       <c r="Y24">
         <v>1.002</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25">
         <v>1979</v>
       </c>
       <c r="B25">
-        <v>1039.0999999999999</v>
+        <v>1039.1</v>
       </c>
       <c r="C25">
-        <v>159.56700000000001</v>
+        <v>159.567</v>
       </c>
       <c r="E25">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="F25">
-        <v>0.35199999999999998</v>
+        <v>0.352</v>
       </c>
       <c r="G25">
-        <v>0.55600000000000005</v>
+        <v>0.556</v>
       </c>
       <c r="H25">
         <v>900.1</v>
@@ -1861,7 +1839,7 @@
         <v>157.512</v>
       </c>
       <c r="K25">
-        <v>8.4000000000000005E-2</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L25">
         <v>0.26</v>
@@ -1873,10 +1851,10 @@
         <v>134</v>
       </c>
       <c r="U25">
-        <v>161.62100000000001</v>
+        <v>161.621</v>
       </c>
       <c r="W25">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="X25">
         <v>0.443</v>
@@ -1885,12 +1863,12 @@
         <v>1.141</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26">
         <v>1980</v>
       </c>
       <c r="B26">
-        <v>976.35500000000002</v>
+        <v>976.355</v>
       </c>
       <c r="C26">
         <v>163.834</v>
@@ -1902,7 +1880,7 @@
         <v>0.43</v>
       </c>
       <c r="G26">
-        <v>0.57099999999999995</v>
+        <v>0.571</v>
       </c>
       <c r="H26">
         <v>822</v>
@@ -1911,10 +1889,10 @@
         <v>164.827</v>
       </c>
       <c r="K26">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="L26">
-        <v>0.36399999999999999</v>
+        <v>0.364</v>
       </c>
       <c r="N26">
         <v>15.355</v>
@@ -1923,19 +1901,19 @@
         <v>139</v>
       </c>
       <c r="U26">
-        <v>162.84200000000001</v>
+        <v>162.842</v>
       </c>
       <c r="W26">
-        <v>7.1999999999999995E-2</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X26">
         <v>0.497</v>
       </c>
       <c r="Y26">
-        <v>1.2989999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.299</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>1981</v>
       </c>
@@ -1943,7 +1921,7 @@
         <v>1240.8</v>
       </c>
       <c r="C27">
-        <v>153.66499999999999</v>
+        <v>153.665</v>
       </c>
       <c r="E27">
         <v>0.113</v>
@@ -1952,7 +1930,7 @@
         <v>0.31</v>
       </c>
       <c r="G27">
-        <v>0.60199999999999998</v>
+        <v>0.602</v>
       </c>
       <c r="H27">
         <v>1011</v>
@@ -1964,7 +1942,7 @@
         <v>0.153</v>
       </c>
       <c r="L27">
-        <v>0.20300000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="N27">
         <v>126.9</v>
@@ -1973,19 +1951,19 @@
         <v>102.9</v>
       </c>
       <c r="U27">
-        <v>161.45500000000001</v>
+        <v>161.455</v>
       </c>
       <c r="W27">
-        <v>7.1999999999999995E-2</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X27">
-        <v>0.41699999999999998</v>
+        <v>0.417</v>
       </c>
       <c r="Y27">
         <v>1.446</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28">
         <v>1982</v>
       </c>
@@ -1993,13 +1971,13 @@
         <v>1100.22</v>
       </c>
       <c r="C28">
-        <v>159.41800000000001</v>
+        <v>159.418</v>
       </c>
       <c r="E28">
         <v>0.09</v>
       </c>
       <c r="F28">
-        <v>0.40300000000000002</v>
+        <v>0.403</v>
       </c>
       <c r="G28">
         <v>0.626</v>
@@ -2008,34 +1986,34 @@
         <v>990</v>
       </c>
       <c r="I28">
-        <v>158.38999999999999</v>
+        <v>158.39</v>
       </c>
       <c r="K28">
         <v>0.107</v>
       </c>
       <c r="L28">
-        <v>0.41499999999999998</v>
+        <v>0.415</v>
       </c>
       <c r="N28">
         <v>32.82</v>
       </c>
       <c r="T28">
-        <v>77.400000000000006</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="U28">
         <v>160.446</v>
       </c>
       <c r="W28">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="X28">
         <v>0.39</v>
       </c>
       <c r="Y28">
-        <v>0.89700000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.897</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1983</v>
       </c>
@@ -2043,16 +2021,16 @@
         <v>1779.77</v>
       </c>
       <c r="C29">
-        <v>159.35300000000001</v>
+        <v>159.353</v>
       </c>
       <c r="E29">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="F29">
-        <v>0.38100000000000001</v>
+        <v>0.381</v>
       </c>
       <c r="G29">
-        <v>0.65600000000000003</v>
+        <v>0.656</v>
       </c>
       <c r="H29">
         <v>1512.47</v>
@@ -2067,7 +2045,7 @@
         <v>0.442</v>
       </c>
       <c r="N29">
-        <v>157.80000000000001</v>
+        <v>157.8</v>
       </c>
       <c r="T29">
         <v>109.5</v>
@@ -2076,16 +2054,16 @@
         <v>158.755</v>
       </c>
       <c r="W29">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="X29">
-        <v>0.32100000000000001</v>
+        <v>0.321</v>
       </c>
       <c r="Y29">
-        <v>0.85199999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.852</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>1984</v>
       </c>
@@ -2093,90 +2071,90 @@
         <v>1213.443</v>
       </c>
       <c r="C30">
-        <v>149.30799999999999</v>
+        <v>149.308</v>
       </c>
       <c r="E30">
         <v>0.12</v>
       </c>
       <c r="F30">
-        <v>0.28199999999999997</v>
+        <v>0.282</v>
       </c>
       <c r="G30">
-        <v>0.65100000000000002</v>
+        <v>0.651</v>
       </c>
       <c r="H30">
-        <v>1053.5899999999999</v>
+        <v>1053.59</v>
       </c>
       <c r="I30">
         <v>137.262</v>
       </c>
       <c r="K30">
-        <v>0.17399999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="L30">
         <v>0.157</v>
       </c>
       <c r="N30">
-        <v>72.352999999999994</v>
+        <v>72.35299999999999</v>
       </c>
       <c r="T30">
         <v>87.5</v>
       </c>
       <c r="U30">
-        <v>161.35300000000001</v>
+        <v>161.353</v>
       </c>
       <c r="W30">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="X30">
-        <v>0.40799999999999997</v>
+        <v>0.408</v>
       </c>
       <c r="Y30">
-        <v>0.84399999999999997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.844</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>1985</v>
       </c>
       <c r="B31">
-        <v>1729.8630000000001</v>
+        <v>1729.863</v>
       </c>
       <c r="C31">
         <v>160.71</v>
       </c>
       <c r="E31">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="F31">
-        <v>0.39600000000000002</v>
+        <v>0.396</v>
       </c>
       <c r="G31">
-        <v>0.66100000000000003</v>
+        <v>0.661</v>
       </c>
       <c r="H31">
         <v>1618.57</v>
       </c>
       <c r="N31">
-        <v>44.625999999999998</v>
+        <v>44.626</v>
       </c>
       <c r="T31">
-        <v>66.667000000000002</v>
+        <v>66.667</v>
       </c>
       <c r="U31">
         <v>160.71</v>
       </c>
       <c r="W31">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="X31">
-        <v>0.39600000000000002</v>
+        <v>0.396</v>
       </c>
       <c r="Y31">
-        <v>0.69599999999999995</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.696</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32">
         <v>1986</v>
       </c>
@@ -2184,16 +2162,16 @@
         <v>1688.568</v>
       </c>
       <c r="C32">
-        <v>158.25800000000001</v>
+        <v>158.258</v>
       </c>
       <c r="E32">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="F32">
-        <v>0.35499999999999998</v>
+        <v>0.355</v>
       </c>
       <c r="G32">
-        <v>0.61399999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="H32">
         <v>1547.94</v>
@@ -2202,31 +2180,31 @@
         <v>156.214</v>
       </c>
       <c r="K32">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="L32">
         <v>0.313</v>
       </c>
       <c r="N32">
-        <v>83.427999999999997</v>
+        <v>83.428</v>
       </c>
       <c r="T32">
         <v>57.2</v>
       </c>
       <c r="U32">
-        <v>160.30199999999999</v>
+        <v>160.302</v>
       </c>
       <c r="W32">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="X32">
-        <v>0.39800000000000002</v>
+        <v>0.398</v>
       </c>
       <c r="Y32">
-        <v>0.98499999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.985</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33">
         <v>1987</v>
       </c>
@@ -2237,10 +2215,10 @@
         <v>159.738</v>
       </c>
       <c r="E33">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="F33">
-        <v>0.40200000000000002</v>
+        <v>0.402</v>
       </c>
       <c r="G33">
         <v>0.622</v>
@@ -2255,10 +2233,10 @@
         <v>0.121</v>
       </c>
       <c r="L33">
-        <v>0.42199999999999999</v>
+        <v>0.422</v>
       </c>
       <c r="N33">
-        <v>63.414000000000001</v>
+        <v>63.414</v>
       </c>
       <c r="T33">
         <v>62.6</v>
@@ -2267,45 +2245,45 @@
         <v>160.822</v>
       </c>
       <c r="W33">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="X33">
-        <v>0.38200000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="Y33">
         <v>1.032</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34">
         <v>1988</v>
       </c>
       <c r="B34">
-        <v>1472.1369999999999</v>
+        <v>1472.137</v>
       </c>
       <c r="C34">
         <v>157.66</v>
       </c>
       <c r="E34">
-        <v>8.4000000000000005E-2</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F34">
         <v>0.309</v>
       </c>
       <c r="G34">
-        <v>0.58099999999999996</v>
+        <v>0.581</v>
       </c>
       <c r="H34">
         <v>1178.78</v>
       </c>
       <c r="I34">
-        <v>153.77199999999999</v>
+        <v>153.772</v>
       </c>
       <c r="K34">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="L34">
-        <v>0.23100000000000001</v>
+        <v>0.231</v>
       </c>
       <c r="N34">
         <v>239.357</v>
@@ -2314,51 +2292,51 @@
         <v>54</v>
       </c>
       <c r="U34">
-        <v>161.54900000000001</v>
+        <v>161.549</v>
       </c>
       <c r="W34">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X34">
-        <v>0.38700000000000001</v>
+        <v>0.387</v>
       </c>
       <c r="Y34">
-        <v>0.77600000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.776</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>1989</v>
       </c>
       <c r="B35">
-        <v>1922.7270000000001</v>
+        <v>1922.727</v>
       </c>
       <c r="C35">
-        <v>154.62700000000001</v>
+        <v>154.627</v>
       </c>
       <c r="E35">
-        <v>8.5999999999999993E-2</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F35">
-        <v>0.23699999999999999</v>
+        <v>0.237</v>
       </c>
       <c r="G35">
-        <v>0.54500000000000004</v>
+        <v>0.545</v>
       </c>
       <c r="H35">
         <v>1799.57</v>
       </c>
       <c r="I35">
-        <v>152.76499999999999</v>
+        <v>152.765</v>
       </c>
       <c r="K35">
         <v>0.11</v>
       </c>
       <c r="L35">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="N35">
-        <v>79.557000000000002</v>
+        <v>79.557</v>
       </c>
       <c r="T35">
         <v>43.6</v>
@@ -2367,16 +2345,16 @@
         <v>156.49</v>
       </c>
       <c r="W35">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="X35">
-        <v>0.27700000000000002</v>
+        <v>0.277</v>
       </c>
       <c r="Y35">
-        <v>0.64500000000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.645</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>1990</v>
       </c>
@@ -2384,16 +2362,16 @@
         <v>1738.607</v>
       </c>
       <c r="C36">
-        <v>157.63300000000001</v>
+        <v>157.633</v>
       </c>
       <c r="E36">
-        <v>8.5000000000000006E-2</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F36">
-        <v>0.38400000000000001</v>
+        <v>0.384</v>
       </c>
       <c r="G36">
-        <v>0.51400000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="H36">
         <v>1645.37</v>
@@ -2405,42 +2383,42 @@
         <v>0.123</v>
       </c>
       <c r="L36">
-        <v>0.23400000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="N36">
-        <v>31.736999999999998</v>
+        <v>31.737</v>
       </c>
       <c r="T36">
         <v>61.5</v>
       </c>
       <c r="U36">
-        <v>164.46700000000001</v>
+        <v>164.467</v>
       </c>
       <c r="W36">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="X36">
-        <v>0.53300000000000003</v>
+        <v>0.533</v>
       </c>
       <c r="Y36">
-        <v>0.63800000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.638</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>1991</v>
       </c>
       <c r="B37">
-        <v>1743.2190000000001</v>
+        <v>1743.219</v>
       </c>
       <c r="C37">
         <v>156.143</v>
       </c>
       <c r="E37">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="F37">
-        <v>0.25700000000000001</v>
+        <v>0.257</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2461,96 +2439,96 @@
         <v>21.689</v>
       </c>
       <c r="O37">
-        <v>158.59100000000001</v>
+        <v>158.591</v>
       </c>
       <c r="Q37">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="R37">
-        <v>0.27500000000000002</v>
+        <v>0.275</v>
       </c>
       <c r="S37">
-        <v>0.70399999999999996</v>
+        <v>0.704</v>
       </c>
       <c r="T37">
         <v>30.1</v>
       </c>
       <c r="U37">
-        <v>160.73599999999999</v>
+        <v>160.736</v>
       </c>
       <c r="W37">
-        <v>7.1999999999999995E-2</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X37">
-        <v>0.33700000000000002</v>
+        <v>0.337</v>
       </c>
       <c r="Y37">
-        <v>0.71799999999999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.718</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38">
         <v>1992</v>
       </c>
       <c r="B38">
-        <v>1557.3989999999999</v>
+        <v>1557.399</v>
       </c>
       <c r="C38">
-        <v>159.64699999999999</v>
+        <v>159.647</v>
       </c>
       <c r="E38">
-        <v>7.4999999999999997E-2</v>
+        <v>0.075</v>
       </c>
       <c r="F38">
-        <v>0.40100000000000002</v>
+        <v>0.401</v>
       </c>
       <c r="G38">
-        <v>0.45200000000000001</v>
+        <v>0.452</v>
       </c>
       <c r="H38">
         <v>1500.83</v>
       </c>
       <c r="I38">
-        <v>151.38300000000001</v>
+        <v>151.383</v>
       </c>
       <c r="K38">
         <v>0.113</v>
       </c>
       <c r="L38">
-        <v>0.20100000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="N38">
-        <v>25.068999999999999</v>
+        <v>25.069</v>
       </c>
       <c r="O38">
         <v>163.423</v>
       </c>
       <c r="Q38">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="R38">
-        <v>0.46400000000000002</v>
+        <v>0.464</v>
       </c>
       <c r="S38">
-        <v>0.40300000000000002</v>
+        <v>0.403</v>
       </c>
       <c r="T38">
         <v>31.5</v>
       </c>
       <c r="U38">
-        <v>164.13499999999999</v>
+        <v>164.135</v>
       </c>
       <c r="W38">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="X38">
-        <v>0.53800000000000003</v>
+        <v>0.538</v>
       </c>
       <c r="Y38">
-        <v>0.59399999999999997</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.594</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>1993</v>
       </c>
@@ -2561,7 +2539,7 @@
         <v>161.268</v>
       </c>
       <c r="E39">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="F39">
         <v>0.503</v>
@@ -2579,66 +2557,66 @@
         <v>0.159</v>
       </c>
       <c r="L39">
-        <v>0.34200000000000003</v>
+        <v>0.342</v>
       </c>
       <c r="M39">
-        <v>1.3779999999999999</v>
+        <v>1.378</v>
       </c>
       <c r="N39">
-        <v>26.960999999999999</v>
+        <v>26.961</v>
       </c>
       <c r="O39">
-        <v>161.44300000000001</v>
+        <v>161.443</v>
       </c>
       <c r="Q39">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="R39">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="S39">
-        <v>0.53700000000000003</v>
+        <v>0.537</v>
       </c>
       <c r="T39">
         <v>41.7</v>
       </c>
       <c r="U39">
-        <v>170.43100000000001</v>
+        <v>170.431</v>
       </c>
       <c r="W39">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="X39">
-        <v>0.75900000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="Y39">
-        <v>0.85799999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.858</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40">
         <v>1994</v>
       </c>
       <c r="B40">
-        <v>2201.9029999999998</v>
+        <v>2201.903</v>
       </c>
       <c r="C40">
-        <v>161.87100000000001</v>
+        <v>161.871</v>
       </c>
       <c r="E40">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="F40">
-        <v>0.46300000000000002</v>
+        <v>0.463</v>
       </c>
       <c r="G40">
-        <v>0.42699999999999999</v>
+        <v>0.427</v>
       </c>
       <c r="H40">
         <v>2128.64</v>
       </c>
       <c r="I40">
-        <v>157.34299999999999</v>
+        <v>157.343</v>
       </c>
       <c r="K40">
         <v>0.154</v>
@@ -2647,19 +2625,19 @@
         <v>0.38</v>
       </c>
       <c r="M40">
-        <v>0.67300000000000004</v>
+        <v>0.673</v>
       </c>
       <c r="N40">
-        <v>32.162999999999997</v>
+        <v>32.163</v>
       </c>
       <c r="O40">
         <v>163</v>
       </c>
       <c r="Q40">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="R40">
-        <v>0.45500000000000002</v>
+        <v>0.455</v>
       </c>
       <c r="S40">
         <v>1.988</v>
@@ -2671,16 +2649,16 @@
         <v>165.27</v>
       </c>
       <c r="W40">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="X40">
-        <v>0.55400000000000005</v>
+        <v>0.554</v>
       </c>
       <c r="Y40">
         <v>1.083</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41">
         <v>1995</v>
       </c>
@@ -2697,7 +2675,7 @@
         <v>0.315</v>
       </c>
       <c r="G41">
-        <v>0.45300000000000001</v>
+        <v>0.453</v>
       </c>
       <c r="H41">
         <v>1841.8</v>
@@ -2706,7 +2684,7 @@
         <v>148.083</v>
       </c>
       <c r="K41">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="L41">
         <v>0.22</v>
@@ -2721,10 +2699,10 @@
         <v>162.035</v>
       </c>
       <c r="Q41">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="R41">
-        <v>0.41099999999999998</v>
+        <v>0.411</v>
       </c>
       <c r="S41">
         <v>1.006</v>
@@ -2736,7 +2714,7 @@
         <v>1.093</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42">
         <v>1996</v>
       </c>
@@ -2750,37 +2728,37 @@
         <v>0.105</v>
       </c>
       <c r="F42">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="G42">
-        <v>0.47399999999999998</v>
+        <v>0.474</v>
       </c>
       <c r="H42">
         <v>1629.19</v>
       </c>
       <c r="I42">
-        <v>146.83500000000001</v>
+        <v>146.835</v>
       </c>
       <c r="K42">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="L42">
         <v>0.188</v>
       </c>
       <c r="M42">
-        <v>0.90200000000000002</v>
+        <v>0.902</v>
       </c>
       <c r="N42">
-        <v>19.155999999999999</v>
+        <v>19.156</v>
       </c>
       <c r="O42">
         <v>159.928</v>
       </c>
       <c r="Q42">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="R42">
-        <v>0.33700000000000002</v>
+        <v>0.337</v>
       </c>
       <c r="S42">
         <v>0.36</v>
@@ -2789,15 +2767,15 @@
         <v>31</v>
       </c>
       <c r="Y42">
-        <v>1.1679999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.168</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>1997</v>
       </c>
       <c r="B43">
-        <v>1512.9069999999999</v>
+        <v>1512.907</v>
       </c>
       <c r="C43">
         <v>160.434</v>
@@ -2806,10 +2784,10 @@
         <v>0.113</v>
       </c>
       <c r="F43">
-        <v>0.48099999999999998</v>
+        <v>0.481</v>
       </c>
       <c r="G43">
-        <v>0.44700000000000001</v>
+        <v>0.447</v>
       </c>
       <c r="H43">
         <v>1482.34</v>
@@ -2821,13 +2799,13 @@
         <v>0.126</v>
       </c>
       <c r="L43">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="M43">
-        <v>1.0660000000000001</v>
+        <v>1.066</v>
       </c>
       <c r="N43">
-        <v>9.5670000000000002</v>
+        <v>9.567</v>
       </c>
       <c r="S43">
         <v>0.34</v>
@@ -2836,19 +2814,19 @@
         <v>21</v>
       </c>
       <c r="U43">
-        <v>167.54499999999999</v>
+        <v>167.545</v>
       </c>
       <c r="W43">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="X43">
-        <v>0.67300000000000004</v>
+        <v>0.673</v>
       </c>
       <c r="Y43">
-        <v>1.0629999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.063</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>1998</v>
       </c>
@@ -2859,7 +2837,7 @@
         <v>151.339</v>
       </c>
       <c r="E44">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="F44">
         <v>0.378</v>
@@ -2871,49 +2849,49 @@
         <v>1789.23</v>
       </c>
       <c r="I44">
-        <v>151.70099999999999</v>
+        <v>151.701</v>
       </c>
       <c r="K44">
         <v>0.128</v>
       </c>
       <c r="L44">
-        <v>0.28599999999999998</v>
+        <v>0.286</v>
       </c>
       <c r="M44">
-        <v>0.88600000000000001</v>
+        <v>0.886</v>
       </c>
       <c r="N44">
-        <v>140.96299999999999</v>
+        <v>140.963</v>
       </c>
       <c r="O44">
-        <v>163.72200000000001</v>
+        <v>163.722</v>
       </c>
       <c r="Q44">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="R44">
         <v>0.504</v>
       </c>
       <c r="S44">
-        <v>0.85899999999999999</v>
+        <v>0.859</v>
       </c>
       <c r="T44">
         <v>15.2</v>
       </c>
       <c r="U44">
-        <v>138.59399999999999</v>
+        <v>138.594</v>
       </c>
       <c r="W44">
         <v>0.22</v>
       </c>
       <c r="X44">
-        <v>0.34399999999999997</v>
+        <v>0.344</v>
       </c>
       <c r="Y44">
         <v>1.248</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45">
         <v>1999</v>
       </c>
@@ -2921,13 +2899,13 @@
         <v>1786.191</v>
       </c>
       <c r="C45">
-        <v>158.61600000000001</v>
+        <v>158.616</v>
       </c>
       <c r="E45">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="F45">
-        <v>0.39700000000000002</v>
+        <v>0.397</v>
       </c>
       <c r="G45">
         <v>0.434</v>
@@ -2936,57 +2914,57 @@
         <v>1731.11</v>
       </c>
       <c r="I45">
-        <v>155.42099999999999</v>
+        <v>155.421</v>
       </c>
       <c r="K45">
         <v>0.17</v>
       </c>
       <c r="L45">
-        <v>0.35299999999999998</v>
+        <v>0.353</v>
       </c>
       <c r="M45">
-        <v>1.6080000000000001</v>
+        <v>1.608</v>
       </c>
       <c r="N45">
         <v>40.881</v>
       </c>
       <c r="O45">
-        <v>161.81100000000001</v>
+        <v>161.811</v>
       </c>
       <c r="Q45">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="R45">
         <v>0.44</v>
       </c>
       <c r="S45">
-        <v>1.4950000000000001</v>
+        <v>1.495</v>
       </c>
       <c r="T45">
         <v>14.2</v>
       </c>
       <c r="Y45">
-        <v>0.73099999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.731</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>2000</v>
       </c>
       <c r="B46">
-        <v>1552.9760000000001</v>
+        <v>1552.976</v>
       </c>
       <c r="C46">
         <v>159.233</v>
       </c>
       <c r="E46">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="F46">
-        <v>0.39700000000000002</v>
+        <v>0.397</v>
       </c>
       <c r="G46">
-        <v>0.44900000000000001</v>
+        <v>0.449</v>
       </c>
       <c r="H46">
         <v>1499.37</v>
@@ -2995,25 +2973,25 @@
         <v>155.791</v>
       </c>
       <c r="K46">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="L46">
-        <v>0.33200000000000002</v>
+        <v>0.332</v>
       </c>
       <c r="M46">
         <v>1.214</v>
       </c>
       <c r="N46">
-        <v>39.906999999999996</v>
+        <v>39.907</v>
       </c>
       <c r="O46">
-        <v>162.67599999999999</v>
+        <v>162.676</v>
       </c>
       <c r="Q46">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="R46">
-        <v>0.46100000000000002</v>
+        <v>0.461</v>
       </c>
       <c r="S46">
         <v>1.026</v>
@@ -3022,10 +3000,10 @@
         <v>13.699</v>
       </c>
       <c r="Y46">
-        <v>0.77500000000000002</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.775</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47">
         <v>2001</v>
       </c>
@@ -3033,55 +3011,55 @@
         <v>1089.425</v>
       </c>
       <c r="C47">
-        <v>157.03100000000001</v>
+        <v>157.031</v>
       </c>
       <c r="E47">
         <v>0.105</v>
       </c>
       <c r="F47">
-        <v>0.38900000000000001</v>
+        <v>0.389</v>
       </c>
       <c r="G47">
-        <v>0.41099999999999998</v>
+        <v>0.411</v>
       </c>
       <c r="H47">
         <v>1036.23</v>
       </c>
       <c r="I47">
-        <v>149.99199999999999</v>
+        <v>149.992</v>
       </c>
       <c r="K47">
-        <v>0.14099999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="L47">
         <v>0.216</v>
       </c>
       <c r="M47">
-        <v>0.49199999999999999</v>
+        <v>0.492</v>
       </c>
       <c r="N47">
-        <v>35.676000000000002</v>
+        <v>35.676</v>
       </c>
       <c r="O47">
         <v>164.07</v>
       </c>
       <c r="Q47">
-        <v>6.9000000000000006E-2</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="R47">
-        <v>0.56299999999999994</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="S47">
-        <v>0.63600000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="T47">
-        <v>17.518000000000001</v>
+        <v>17.518</v>
       </c>
       <c r="Y47">
-        <v>0.92400000000000004</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.924</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>2002</v>
       </c>
@@ -3089,46 +3067,46 @@
         <v>1018.957</v>
       </c>
       <c r="C48">
-        <v>162.60900000000001</v>
+        <v>162.609</v>
       </c>
       <c r="E48">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="F48">
-        <v>0.57199999999999995</v>
+        <v>0.572</v>
       </c>
       <c r="G48">
         <v>0.372</v>
       </c>
       <c r="H48">
-        <v>907.87400000000002</v>
+        <v>907.874</v>
       </c>
       <c r="I48">
-        <v>151.23500000000001</v>
+        <v>151.235</v>
       </c>
       <c r="K48">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="L48">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="M48">
-        <v>1.0009999999999999</v>
+        <v>1.001</v>
       </c>
       <c r="N48">
-        <v>93.394000000000005</v>
+        <v>93.39400000000001</v>
       </c>
       <c r="O48">
         <v>163.95</v>
       </c>
       <c r="Q48">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="R48">
         <v>0.52</v>
       </c>
       <c r="S48">
-        <v>0.89400000000000002</v>
+        <v>0.894</v>
       </c>
       <c r="T48">
         <v>17.689</v>
@@ -3137,7 +3115,7 @@
         <v>172.642</v>
       </c>
       <c r="W48">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="X48">
         <v>1</v>
@@ -3146,21 +3124,21 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49">
         <v>2003</v>
       </c>
       <c r="B49">
-        <v>850.07500000000005</v>
+        <v>850.075</v>
       </c>
       <c r="C49">
         <v>159.614</v>
       </c>
       <c r="E49">
-        <v>0.11700000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="F49">
-        <v>0.45200000000000001</v>
+        <v>0.452</v>
       </c>
       <c r="G49">
         <v>0.34</v>
@@ -3169,184 +3147,184 @@
         <v>815.601</v>
       </c>
       <c r="I49">
-        <v>153.25200000000001</v>
+        <v>153.252</v>
       </c>
       <c r="K49">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="L49">
-        <v>0.35699999999999998</v>
+        <v>0.357</v>
       </c>
       <c r="M49">
-        <v>0.55800000000000005</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="N49">
-        <v>20.655000000000001</v>
+        <v>20.655</v>
       </c>
       <c r="O49">
-        <v>165.97499999999999</v>
+        <v>165.975</v>
       </c>
       <c r="Q49">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R49">
-        <v>0.54700000000000004</v>
+        <v>0.547</v>
       </c>
       <c r="S49">
-        <v>0.97399999999999998</v>
+        <v>0.974</v>
       </c>
       <c r="T49">
-        <v>13.819000000000001</v>
+        <v>13.819</v>
       </c>
       <c r="Y49">
-        <v>0.79600000000000004</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.796</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>2004</v>
       </c>
       <c r="B50">
-        <v>848.46600000000001</v>
+        <v>848.466</v>
       </c>
       <c r="C50">
         <v>159.279</v>
       </c>
       <c r="E50">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="F50">
-        <v>0.39600000000000002</v>
+        <v>0.396</v>
       </c>
       <c r="G50">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="H50">
-        <v>812.33100000000002</v>
+        <v>812.331</v>
       </c>
       <c r="I50">
-        <v>158.69399999999999</v>
+        <v>158.694</v>
       </c>
       <c r="K50">
         <v>0.12</v>
       </c>
       <c r="L50">
-        <v>0.42299999999999999</v>
+        <v>0.423</v>
       </c>
       <c r="M50">
-        <v>0.96799999999999997</v>
+        <v>0.968</v>
       </c>
       <c r="N50">
         <v>22.186</v>
       </c>
       <c r="O50">
-        <v>159.86500000000001</v>
+        <v>159.865</v>
       </c>
       <c r="Q50">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="R50">
-        <v>0.36799999999999999</v>
+        <v>0.368</v>
       </c>
       <c r="S50">
-        <v>1.4630000000000001</v>
+        <v>1.463</v>
       </c>
       <c r="T50">
         <v>13.949</v>
       </c>
       <c r="Y50">
-        <v>0.85399999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.854</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51">
         <v>2005</v>
       </c>
       <c r="B51">
-        <v>769.80799999999999</v>
+        <v>769.808</v>
       </c>
       <c r="C51">
-        <v>159.11600000000001</v>
+        <v>159.116</v>
       </c>
       <c r="E51">
         <v>0.113</v>
       </c>
       <c r="F51">
-        <v>0.38200000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="G51">
-        <v>0.33400000000000002</v>
+        <v>0.334</v>
       </c>
       <c r="H51">
-        <v>741.59100000000001</v>
+        <v>741.591</v>
       </c>
       <c r="I51">
         <v>155.876</v>
       </c>
       <c r="K51">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="L51">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="M51">
-        <v>1.2470000000000001</v>
+        <v>1.247</v>
       </c>
       <c r="N51">
-        <v>16.178999999999998</v>
+        <v>16.179</v>
       </c>
       <c r="O51">
-        <v>162.35499999999999</v>
+        <v>162.355</v>
       </c>
       <c r="Q51">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="R51">
-        <v>0.42599999999999999</v>
+        <v>0.426</v>
       </c>
       <c r="S51">
-        <v>1.4810000000000001</v>
+        <v>1.481</v>
       </c>
       <c r="T51">
         <v>12.038</v>
       </c>
       <c r="Y51">
-        <v>0.93100000000000005</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.931</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52">
         <v>2006</v>
       </c>
       <c r="B52">
-        <v>618.64300000000003</v>
+        <v>618.643</v>
       </c>
       <c r="C52">
-        <v>162.54599999999999</v>
+        <v>162.546</v>
       </c>
       <c r="E52">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="F52">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="G52">
-        <v>0.33900000000000002</v>
+        <v>0.339</v>
       </c>
       <c r="H52">
-        <v>580.26800000000003</v>
+        <v>580.268</v>
       </c>
       <c r="I52">
         <v>153.648</v>
       </c>
       <c r="K52">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="L52">
-        <v>0.32300000000000001</v>
+        <v>0.323</v>
       </c>
       <c r="M52">
-        <v>0.80400000000000005</v>
+        <v>0.804</v>
       </c>
       <c r="N52">
         <v>25.994</v>
@@ -3355,10 +3333,10 @@
         <v>161.971</v>
       </c>
       <c r="Q52">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="R52">
-        <v>0.45400000000000001</v>
+        <v>0.454</v>
       </c>
       <c r="S52">
         <v>1.419</v>
@@ -3370,27 +3348,27 @@
         <v>172.018</v>
       </c>
       <c r="W52">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.1659999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.166</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53">
         <v>2007</v>
       </c>
       <c r="B53">
-        <v>766.75699999999995</v>
+        <v>766.7569999999999</v>
       </c>
       <c r="C53">
-        <v>159.61600000000001</v>
+        <v>159.616</v>
       </c>
       <c r="E53">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="F53">
         <v>0.43</v>
@@ -3399,34 +3377,34 @@
         <v>0.34</v>
       </c>
       <c r="H53">
-        <v>719.08299999999997</v>
+        <v>719.083</v>
       </c>
       <c r="I53">
-        <v>156.88999999999999</v>
+        <v>156.89</v>
       </c>
       <c r="K53">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="L53">
         <v>0.41</v>
       </c>
       <c r="M53">
-        <v>0.60699999999999998</v>
+        <v>0.607</v>
       </c>
       <c r="N53">
-        <v>37.392000000000003</v>
+        <v>37.392</v>
       </c>
       <c r="O53">
-        <v>162.34299999999999</v>
+        <v>162.343</v>
       </c>
       <c r="Q53">
-        <v>5.3999999999999999E-2</v>
+        <v>0.054</v>
       </c>
       <c r="R53">
         <v>0.45</v>
       </c>
       <c r="S53">
-        <v>1.6240000000000001</v>
+        <v>1.624</v>
       </c>
       <c r="T53">
         <v>10.282</v>
@@ -3435,95 +3413,95 @@
         <v>1.085</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54">
         <v>2008</v>
       </c>
       <c r="B54">
-        <v>737.91099999999994</v>
+        <v>737.9109999999999</v>
       </c>
       <c r="C54">
         <v>164.89</v>
       </c>
       <c r="E54">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="F54">
-        <v>0.61899999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="G54">
-        <v>0.34499999999999997</v>
+        <v>0.345</v>
       </c>
       <c r="H54">
-        <v>687.66099999999994</v>
+        <v>687.6609999999999</v>
       </c>
       <c r="I54">
-        <v>154.63300000000001</v>
+        <v>154.633</v>
       </c>
       <c r="K54">
         <v>0.127</v>
       </c>
       <c r="L54">
-        <v>0.28299999999999997</v>
+        <v>0.283</v>
       </c>
       <c r="M54">
-        <v>0.59099999999999997</v>
+        <v>0.591</v>
       </c>
       <c r="N54">
-        <v>38.271000000000001</v>
+        <v>38.271</v>
       </c>
       <c r="O54">
-        <v>164.29599999999999</v>
+        <v>164.296</v>
       </c>
       <c r="Q54">
-        <v>5.8000000000000003E-2</v>
+        <v>0.058</v>
       </c>
       <c r="R54">
-        <v>0.57399999999999995</v>
+        <v>0.574</v>
       </c>
       <c r="S54">
         <v>1.165</v>
       </c>
       <c r="T54">
-        <v>11.978999999999999</v>
+        <v>11.979</v>
       </c>
       <c r="U54">
-        <v>175.74100000000001</v>
+        <v>175.741</v>
       </c>
       <c r="W54">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="X54">
         <v>1</v>
       </c>
       <c r="Y54">
-        <v>0.84799999999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.848</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55">
         <v>2009</v>
       </c>
       <c r="B55">
-        <v>788.02599999999995</v>
+        <v>788.026</v>
       </c>
       <c r="C55">
-        <v>163.38900000000001</v>
+        <v>163.389</v>
       </c>
       <c r="E55">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="F55">
-        <v>0.55500000000000005</v>
+        <v>0.555</v>
       </c>
       <c r="G55">
-        <v>0.36099999999999999</v>
+        <v>0.361</v>
       </c>
       <c r="H55">
-        <v>726.16200000000003</v>
+        <v>726.162</v>
       </c>
       <c r="I55">
-        <v>154.07599999999999</v>
+        <v>154.076</v>
       </c>
       <c r="K55">
         <v>0.106</v>
@@ -3532,122 +3510,122 @@
         <v>0.183</v>
       </c>
       <c r="M55">
-        <v>1.0169999999999999</v>
+        <v>1.017</v>
       </c>
       <c r="N55">
-        <v>47.656999999999996</v>
+        <v>47.657</v>
       </c>
       <c r="O55">
         <v>162.59</v>
       </c>
       <c r="Q55">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="R55">
-        <v>0.48099999999999998</v>
+        <v>0.481</v>
       </c>
       <c r="S55">
-        <v>0.99199999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="T55">
-        <v>14.207000000000001</v>
+        <v>14.207</v>
       </c>
       <c r="U55">
         <v>173.5</v>
       </c>
       <c r="W55">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="X55">
         <v>1</v>
       </c>
       <c r="Y55">
-        <v>0.63400000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.634</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56">
         <v>2010</v>
       </c>
       <c r="B56">
-        <v>531.37599999999998</v>
+        <v>531.376</v>
       </c>
       <c r="C56">
         <v>164.364</v>
       </c>
       <c r="E56">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="F56">
         <v>0.59</v>
       </c>
       <c r="G56">
-        <v>0.36199999999999999</v>
+        <v>0.362</v>
       </c>
       <c r="H56">
-        <v>494.94600000000003</v>
+        <v>494.946</v>
       </c>
       <c r="I56">
         <v>153.065</v>
       </c>
       <c r="K56">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="L56">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="M56">
-        <v>0.65600000000000003</v>
+        <v>0.656</v>
       </c>
       <c r="N56">
-        <v>21.795000000000002</v>
+        <v>21.795</v>
       </c>
       <c r="S56">
-        <v>0.63600000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="T56">
         <v>14.635</v>
       </c>
       <c r="U56">
-        <v>175.66300000000001</v>
+        <v>175.663</v>
       </c>
       <c r="W56">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="X56">
         <v>1</v>
       </c>
       <c r="Y56">
-        <v>0.94799999999999995</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57">
         <v>2011</v>
       </c>
       <c r="B57">
-        <v>550.04399999999998</v>
+        <v>550.044</v>
       </c>
       <c r="C57">
         <v>163.739</v>
       </c>
       <c r="E57">
-        <v>7.0999999999999994E-2</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F57">
-        <v>0.58099999999999996</v>
+        <v>0.581</v>
       </c>
       <c r="G57">
-        <v>0.36899999999999999</v>
+        <v>0.369</v>
       </c>
       <c r="H57">
         <v>500.904</v>
       </c>
       <c r="I57">
-        <v>152.87100000000001</v>
+        <v>152.871</v>
       </c>
       <c r="K57">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="L57">
         <v>0.184</v>
@@ -3656,33 +3634,33 @@
         <v>1.64</v>
       </c>
       <c r="N57">
-        <v>9.4960000000000004</v>
+        <v>9.496</v>
       </c>
       <c r="T57">
-        <v>39.643999999999998</v>
+        <v>39.644</v>
       </c>
       <c r="U57">
         <v>174.607</v>
       </c>
       <c r="W57">
-        <v>4.2999999999999997E-2</v>
+        <v>0.043</v>
       </c>
       <c r="X57">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="Y57">
         <v>1.071</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58">
         <v>2012</v>
       </c>
       <c r="B58">
-        <v>489.06799999999998</v>
+        <v>489.068</v>
       </c>
       <c r="C58">
-        <v>150.09100000000001</v>
+        <v>150.091</v>
       </c>
       <c r="E58">
         <v>0.09</v>
@@ -3694,10 +3672,10 @@
         <v>0.371</v>
       </c>
       <c r="H58">
-        <v>461.17599999999999</v>
+        <v>461.176</v>
       </c>
       <c r="I58">
-        <v>150.09100000000001</v>
+        <v>150.091</v>
       </c>
       <c r="K58">
         <v>0.09</v>
@@ -3709,48 +3687,48 @@
         <v>1.526</v>
       </c>
       <c r="N58">
-        <v>26.373999999999999</v>
+        <v>26.374</v>
       </c>
       <c r="T58">
-        <v>1.5189999999999999</v>
+        <v>1.519</v>
       </c>
       <c r="Y58">
-        <v>1.0089999999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.009</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59">
         <v>2013</v>
       </c>
       <c r="B59">
-        <v>660.65899999999999</v>
+        <v>660.659</v>
       </c>
       <c r="C59">
         <v>152.04</v>
       </c>
       <c r="E59">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="F59">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="G59">
-        <v>0.39900000000000002</v>
+        <v>0.399</v>
       </c>
       <c r="H59">
-        <v>530.39700000000005</v>
+        <v>530.397</v>
       </c>
       <c r="I59">
         <v>152.04</v>
       </c>
       <c r="K59">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="L59">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="M59">
-        <v>0.91900000000000004</v>
+        <v>0.919</v>
       </c>
       <c r="N59">
         <v>126.292</v>
@@ -3759,10 +3737,10 @@
         <v>3.97</v>
       </c>
       <c r="Y59">
-        <v>1.3109999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.311</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60">
         <v>2014</v>
       </c>
@@ -3770,40 +3748,40 @@
         <v>474.85</v>
       </c>
       <c r="C60">
-        <v>156.47900000000001</v>
+        <v>156.479</v>
       </c>
       <c r="E60">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="F60">
         <v>0.443</v>
       </c>
       <c r="G60">
-        <v>0.42199999999999999</v>
+        <v>0.422</v>
       </c>
       <c r="H60">
-        <v>449.93099999999998</v>
+        <v>449.931</v>
       </c>
       <c r="I60">
         <v>152.142</v>
       </c>
       <c r="K60">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="L60">
-        <v>0.13200000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="M60">
-        <v>0.98399999999999999</v>
+        <v>0.984</v>
       </c>
       <c r="N60">
-        <v>22.547999999999998</v>
+        <v>22.548</v>
       </c>
       <c r="O60">
         <v>160.816</v>
       </c>
       <c r="Q60">
-        <v>0.27500000000000002</v>
+        <v>0.275</v>
       </c>
       <c r="R60">
         <v>0.755</v>
@@ -3812,10 +3790,10 @@
         <v>2.371</v>
       </c>
       <c r="Y60">
-        <v>0.94199999999999995</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.9419999999999999</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61">
         <v>2015</v>
       </c>
@@ -3823,119 +3801,119 @@
         <v>505.767</v>
       </c>
       <c r="C61">
-        <v>152.02699999999999</v>
+        <v>152.027</v>
       </c>
       <c r="E61">
-        <v>8.4000000000000005E-2</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F61">
         <v>0.129</v>
       </c>
       <c r="G61">
-        <v>0.44800000000000001</v>
+        <v>0.448</v>
       </c>
       <c r="H61">
-        <v>485.97800000000001</v>
+        <v>485.978</v>
       </c>
       <c r="I61">
-        <v>152.02699999999999</v>
+        <v>152.027</v>
       </c>
       <c r="K61">
-        <v>8.4000000000000005E-2</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L61">
         <v>0.129</v>
       </c>
       <c r="M61">
-        <v>1.0329999999999999</v>
+        <v>1.033</v>
       </c>
       <c r="N61">
         <v>16.544</v>
       </c>
       <c r="T61">
-        <v>3.2440000000000002</v>
+        <v>3.244</v>
       </c>
       <c r="Y61">
-        <v>0.80200000000000005</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62">
         <v>2016</v>
       </c>
       <c r="B62">
-        <v>485.56299999999999</v>
+        <v>485.563</v>
       </c>
       <c r="C62">
-        <v>153.37299999999999</v>
+        <v>153.373</v>
       </c>
       <c r="E62">
-        <v>8.5000000000000006E-2</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F62">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="G62">
-        <v>0.45400000000000001</v>
+        <v>0.454</v>
       </c>
       <c r="H62">
         <v>464.178</v>
       </c>
       <c r="I62">
-        <v>153.37299999999999</v>
+        <v>153.373</v>
       </c>
       <c r="K62">
-        <v>8.5000000000000006E-2</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L62">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="M62">
-        <v>0.98399999999999999</v>
+        <v>0.984</v>
       </c>
       <c r="N62">
-        <v>19.437000000000001</v>
+        <v>19.437</v>
       </c>
       <c r="T62">
         <v>1.948</v>
       </c>
       <c r="Y62">
-        <v>0.73499999999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.735</v>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63">
         <v>2017</v>
       </c>
       <c r="B63">
-        <v>493.60899999999998</v>
+        <v>493.609</v>
       </c>
       <c r="C63">
-        <v>166.49799999999999</v>
+        <v>166.498</v>
       </c>
       <c r="E63">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="F63">
-        <v>0.61899999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="G63">
-        <v>0.48099999999999998</v>
+        <v>0.481</v>
       </c>
       <c r="H63">
-        <v>467.35700000000003</v>
+        <v>467.357</v>
       </c>
       <c r="I63">
-        <v>154.05600000000001</v>
+        <v>154.056</v>
       </c>
       <c r="K63">
         <v>0.09</v>
       </c>
       <c r="L63">
-        <v>0.17599999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="M63">
-        <v>0.90200000000000002</v>
+        <v>0.902</v>
       </c>
       <c r="N63">
         <v>20.259</v>
@@ -3944,25 +3922,25 @@
         <v>172.685</v>
       </c>
       <c r="Q63">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="R63">
-        <v>0.70399999999999996</v>
+        <v>0.704</v>
       </c>
       <c r="T63">
-        <v>5.9930000000000003</v>
+        <v>5.993</v>
       </c>
       <c r="U63">
-        <v>172.75299999999999</v>
+        <v>172.753</v>
       </c>
       <c r="W63">
-        <v>4.2999999999999997E-2</v>
+        <v>0.043</v>
       </c>
       <c r="X63">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="Y63">
-        <v>0.67300000000000004</v>
+        <v>0.673</v>
       </c>
     </row>
   </sheetData>

--- a/Indicator_4/Real_data/White_Marlin_Atl.xlsx
+++ b/Indicator_4/Real_data/White_Marlin_Atl.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
+    <sheet name="B_BMSY" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>172.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -498,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>172.1</t>
+          <t>0.932</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2447,9 +2448,6 @@
       <c r="R37">
         <v>0.275</v>
       </c>
-      <c r="S37">
-        <v>0.704</v>
-      </c>
       <c r="T37">
         <v>30.1</v>
       </c>
@@ -2509,9 +2507,6 @@
       <c r="R38">
         <v>0.464</v>
       </c>
-      <c r="S38">
-        <v>0.403</v>
-      </c>
       <c r="T38">
         <v>31.5</v>
       </c>
@@ -2574,9 +2569,6 @@
       <c r="R39">
         <v>0.409</v>
       </c>
-      <c r="S39">
-        <v>0.537</v>
-      </c>
       <c r="T39">
         <v>41.7</v>
       </c>
@@ -2639,9 +2631,6 @@
       <c r="R40">
         <v>0.455</v>
       </c>
-      <c r="S40">
-        <v>1.988</v>
-      </c>
       <c r="T40">
         <v>41.1</v>
       </c>
@@ -2704,9 +2693,6 @@
       <c r="R41">
         <v>0.411</v>
       </c>
-      <c r="S41">
-        <v>1.006</v>
-      </c>
       <c r="T41">
         <v>31</v>
       </c>
@@ -2760,9 +2746,6 @@
       <c r="R42">
         <v>0.337</v>
       </c>
-      <c r="S42">
-        <v>0.36</v>
-      </c>
       <c r="T42">
         <v>31</v>
       </c>
@@ -2807,9 +2790,6 @@
       <c r="N43">
         <v>9.567</v>
       </c>
-      <c r="S43">
-        <v>0.34</v>
-      </c>
       <c r="T43">
         <v>21</v>
       </c>
@@ -2872,9 +2852,6 @@
       <c r="R44">
         <v>0.504</v>
       </c>
-      <c r="S44">
-        <v>0.859</v>
-      </c>
       <c r="T44">
         <v>15.2</v>
       </c>
@@ -2937,9 +2914,6 @@
       <c r="R45">
         <v>0.44</v>
       </c>
-      <c r="S45">
-        <v>1.495</v>
-      </c>
       <c r="T45">
         <v>14.2</v>
       </c>
@@ -2993,9 +2967,6 @@
       <c r="R46">
         <v>0.461</v>
       </c>
-      <c r="S46">
-        <v>1.026</v>
-      </c>
       <c r="T46">
         <v>13.699</v>
       </c>
@@ -3049,9 +3020,6 @@
       <c r="R47">
         <v>0.5629999999999999</v>
       </c>
-      <c r="S47">
-        <v>0.636</v>
-      </c>
       <c r="T47">
         <v>17.518</v>
       </c>
@@ -3105,9 +3073,6 @@
       <c r="R48">
         <v>0.52</v>
       </c>
-      <c r="S48">
-        <v>0.894</v>
-      </c>
       <c r="T48">
         <v>17.689</v>
       </c>
@@ -3170,9 +3135,6 @@
       <c r="R49">
         <v>0.547</v>
       </c>
-      <c r="S49">
-        <v>0.974</v>
-      </c>
       <c r="T49">
         <v>13.819</v>
       </c>
@@ -3226,9 +3188,6 @@
       <c r="R50">
         <v>0.368</v>
       </c>
-      <c r="S50">
-        <v>1.463</v>
-      </c>
       <c r="T50">
         <v>13.949</v>
       </c>
@@ -3282,9 +3241,6 @@
       <c r="R51">
         <v>0.426</v>
       </c>
-      <c r="S51">
-        <v>1.481</v>
-      </c>
       <c r="T51">
         <v>12.038</v>
       </c>
@@ -3338,9 +3294,6 @@
       <c r="R52">
         <v>0.454</v>
       </c>
-      <c r="S52">
-        <v>1.419</v>
-      </c>
       <c r="T52">
         <v>12.381</v>
       </c>
@@ -3403,9 +3356,6 @@
       <c r="R53">
         <v>0.45</v>
       </c>
-      <c r="S53">
-        <v>1.624</v>
-      </c>
       <c r="T53">
         <v>10.282</v>
       </c>
@@ -3459,9 +3409,6 @@
       <c r="R54">
         <v>0.574</v>
       </c>
-      <c r="S54">
-        <v>1.165</v>
-      </c>
       <c r="T54">
         <v>11.979</v>
       </c>
@@ -3524,9 +3471,6 @@
       <c r="R55">
         <v>0.481</v>
       </c>
-      <c r="S55">
-        <v>0.992</v>
-      </c>
       <c r="T55">
         <v>14.207</v>
       </c>
@@ -3580,9 +3524,6 @@
       <c r="N56">
         <v>21.795</v>
       </c>
-      <c r="S56">
-        <v>0.636</v>
-      </c>
       <c r="T56">
         <v>14.635</v>
       </c>
@@ -3941,6 +3882,839 @@
       </c>
       <c r="Y63">
         <v>0.673</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C63"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StDev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSB_1956</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>3.298742153584064</v>
+      </c>
+      <c r="C2">
+        <v>0.2500036297991995</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSB_1957</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>3.296109339231354</v>
+      </c>
+      <c r="C3">
+        <v>0.2499958862275739</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SSB_1958</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>3.27416599313726</v>
+      </c>
+      <c r="C4">
+        <v>0.2499232902435837</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSB_1959</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3.254071424768782</v>
+      </c>
+      <c r="C5">
+        <v>0.2498008450172536</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSB_1960</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3.242828726714838</v>
+      </c>
+      <c r="C6">
+        <v>0.2496454896115147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSB_1961</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>3.205528910140691</v>
+      </c>
+      <c r="C7">
+        <v>0.2493710767920319</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSB_1962</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>3.100801943636478</v>
+      </c>
+      <c r="C8">
+        <v>0.248742395570677</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSB_1963</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2.837626982475329</v>
+      </c>
+      <c r="C9">
+        <v>0.2470784956176224</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SSB_1964</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2.526954888855549</v>
+      </c>
+      <c r="C10">
+        <v>0.2440793135323754</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SSB_1965</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2.102515208858646</v>
+      </c>
+      <c r="C11">
+        <v>0.2384187626740489</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SSB_1966</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1.578125378104083</v>
+      </c>
+      <c r="C12">
+        <v>0.2280951297774207</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SSB_1967</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>1.285215101900563</v>
+      </c>
+      <c r="C13">
+        <v>0.21761807736796</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SSB_1968</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>1.270599110457209</v>
+      </c>
+      <c r="C14">
+        <v>0.2124855412998553</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SSB_1969</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>1.188962506594135</v>
+      </c>
+      <c r="C15">
+        <v>0.2046461429753706</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SSB_1970</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>1.085034095913814</v>
+      </c>
+      <c r="C16">
+        <v>0.1962066178499005</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SSB_1971</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0.9985384008556647</v>
+      </c>
+      <c r="C17">
+        <v>0.188710356543076</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SSB_1972</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.9006209376497293</v>
+      </c>
+      <c r="C18">
+        <v>0.1811022974209067</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SSB_1973</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0.8017742458487197</v>
+      </c>
+      <c r="C19">
+        <v>0.1738838367461512</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SSB_1974</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0.7496648485405787</v>
+      </c>
+      <c r="C20">
+        <v>0.1693059339957314</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SSB_1975</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.7066589876248045</v>
+      </c>
+      <c r="C21">
+        <v>0.1656611316261984</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SSB_1976</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.6630965574984391</v>
+      </c>
+      <c r="C22">
+        <v>0.1626062926198923</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SSB_1977</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.6088963958513814</v>
+      </c>
+      <c r="C23">
+        <v>0.1597005173673793</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SSB_1978</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>0.6256660681531098</v>
+      </c>
+      <c r="C24">
+        <v>0.1612390682547441</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SSB_1979</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>0.6591376565048421</v>
+      </c>
+      <c r="C25">
+        <v>0.164158394757602</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SSB_1980</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>0.6851270187733215</v>
+      </c>
+      <c r="C26">
+        <v>0.1669180100956815</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SSB_1981</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>0.7181001147016547</v>
+      </c>
+      <c r="C27">
+        <v>0.1697415098996723</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SSB_1982</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>0.7131345493967274</v>
+      </c>
+      <c r="C28">
+        <v>0.1701078776322094</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SSB_1983</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>0.7238400371691437</v>
+      </c>
+      <c r="C29">
+        <v>0.1702961432173572</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SSB_1984</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>0.6721710554972098</v>
+      </c>
+      <c r="C30">
+        <v>0.1652173281774052</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SSB_1985</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>0.6809503298277539</v>
+      </c>
+      <c r="C31">
+        <v>0.1616175353179462</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SSB_1986</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>0.63626992154794</v>
+      </c>
+      <c r="C32">
+        <v>0.153648916141959</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SSB_1987</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>0.5962888932984227</v>
+      </c>
+      <c r="C33">
+        <v>0.1462083117561937</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SSB_1988</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>0.5622849343974291</v>
+      </c>
+      <c r="C34">
+        <v>0.1402022040140739</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SSB_1989</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>0.5472140081210708</v>
+      </c>
+      <c r="C35">
+        <v>0.1356635030950088</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SSB_1990</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>0.4950029764353436</v>
+      </c>
+      <c r="C36">
+        <v>0.1285389332262139</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SSB_1991</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>0.4746804566771366</v>
+      </c>
+      <c r="C37">
+        <v>0.1237263034608925</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SSB_1992</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>0.4676899473921103</v>
+      </c>
+      <c r="C38">
+        <v>0.1203167120794878</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SSB_1993</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>0.4958354103850975</v>
+      </c>
+      <c r="C39">
+        <v>0.1184993926136006</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SSB_1994</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>0.5193081118752511</v>
+      </c>
+      <c r="C40">
+        <v>0.116045648354733</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SSB_1995</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>0.4896115146910073</v>
+      </c>
+      <c r="C41">
+        <v>0.1124836054069489</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SSB_1996</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0.473875609201299</v>
+      </c>
+      <c r="C42">
+        <v>0.1127754412625894</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SSB_1997</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>0.4748614626638854</v>
+      </c>
+      <c r="C43">
+        <v>0.1126984895195598</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SSB_1998</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0.4917264776912541</v>
+      </c>
+      <c r="C44">
+        <v>0.1098420795361601</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SSB_1999</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0.450384032755308</v>
+      </c>
+      <c r="C45">
+        <v>0.1038040295610847</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SSB_2000</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>0.4074981971997309</v>
+      </c>
+      <c r="C46">
+        <v>0.09832980839499959</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SSB_2001</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>0.372248491213466</v>
+      </c>
+      <c r="C47">
+        <v>0.09493376826393964</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SSB_2002</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>0.3704510146498696</v>
+      </c>
+      <c r="C48">
+        <v>0.09496958228270813</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SSB_2003</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0.3654956127827009</v>
+      </c>
+      <c r="C49">
+        <v>0.09608610851647686</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SSB_2004</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>0.3712790928405841</v>
+      </c>
+      <c r="C50">
+        <v>0.09866713773394056</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SSB_2005</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0.37258824041854</v>
+      </c>
+      <c r="C51">
+        <v>0.1015191919583009</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SSB_2006</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.3773268222801914</v>
+      </c>
+      <c r="C52">
+        <v>0.1049583057065283</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SSB_2007</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>0.3947847045101465</v>
+      </c>
+      <c r="C53">
+        <v>0.1090865973294357</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SSB_2008</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>0.3967767383108367</v>
+      </c>
+      <c r="C54">
+        <v>0.1123069551792395</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SSB_2009</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>0.4034996104015526</v>
+      </c>
+      <c r="C55">
+        <v>0.115861254555398</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SSB_2010</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>0.4065186353890903</v>
+      </c>
+      <c r="C56">
+        <v>0.119719489117862</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SSB_2011</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>0.4367776094626445</v>
+      </c>
+      <c r="C57">
+        <v>0.1258141639604497</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SSB_2012</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>0.4620385920250892</v>
+      </c>
+      <c r="C58">
+        <v>0.1318604414803773</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SSB_2013</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>0.4904681473020912</v>
+      </c>
+      <c r="C59">
+        <v>0.138134670390034</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SSB_2014</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>0.4975583550717974</v>
+      </c>
+      <c r="C60">
+        <v>0.1436630965574985</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SSB_2015</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.5264176785740213</v>
+      </c>
+      <c r="C61">
+        <v>0.1503254719948892</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SSB_2016</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>0.556090077096935</v>
+      </c>
+      <c r="C62">
+        <v>0.1571891802945461</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SSB_2017</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>0.5996476674910344</v>
+      </c>
+      <c r="C63">
+        <v>0.1643418206104838</v>
       </c>
     </row>
   </sheetData>
